--- a/public/flie/Template Aircraft Sched-Mapping.xlsx
+++ b/public/flie/Template Aircraft Sched-Mapping.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e55ca4bad86d753/Desktop/ภาษี/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e55ca4bad86d753/Desktop/Images/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="233" documentId="11_C026B8655C66716B89AF53C5EB1F5D9AB1CC498E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76805127-0EB6-4095-B64E-6C1BFE3B79E8}"/>
+  <xr:revisionPtr revIDLastSave="253" documentId="11_C026B8655C66716B89AF53C5EB1F5D9AB1CC498E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77E9AAF8-E90A-437E-8311-1633E45149C9}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="854" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="13022026" sheetId="1" r:id="rId1"/>
+    <sheet name="16032026" sheetId="1" r:id="rId1"/>
     <sheet name="_Temple" sheetId="2" r:id="rId2"/>
     <sheet name="_ROUTE_LIST" sheetId="3" r:id="rId3"/>
     <sheet name="_MAINTENANCE_STATUS" sheetId="4" r:id="rId4"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="409">
   <si>
     <t>AIRLINE</t>
   </si>
@@ -728,132 +728,9 @@
     <t>CCU</t>
   </si>
   <si>
-    <t>9 Air</t>
-  </si>
-  <si>
-    <t>Air Astana</t>
-  </si>
-  <si>
-    <t>Air India</t>
-  </si>
-  <si>
-    <t>Air India Express</t>
-  </si>
-  <si>
-    <t>Air Macau</t>
-  </si>
-  <si>
-    <t>Akasa Air</t>
-  </si>
-  <si>
-    <t>Cebu Pacific</t>
-  </si>
-  <si>
-    <t>Afcom</t>
-  </si>
-  <si>
-    <t>Central Airlines</t>
-  </si>
-  <si>
-    <t>China Central Longhao Airlines</t>
-  </si>
-  <si>
-    <t>Druk Air</t>
-  </si>
-  <si>
-    <t>Firefly</t>
-  </si>
-  <si>
-    <t>Indigo</t>
-  </si>
-  <si>
-    <t>Jiangsu Jingdong Cargo Airlines</t>
-  </si>
-  <si>
-    <t>K-Mile Air</t>
-  </si>
-  <si>
-    <t>Malaysia Airlines</t>
-  </si>
-  <si>
-    <t>MAQUARIE</t>
-  </si>
-  <si>
-    <t>Merx Aviation Servicing Limited</t>
-  </si>
-  <si>
-    <t>Myanmar National Airlines</t>
-  </si>
-  <si>
-    <t>NOK Air</t>
-  </si>
-  <si>
-    <t>OK Airways</t>
-  </si>
-  <si>
-    <t>Philippine Airlines</t>
-  </si>
-  <si>
-    <t>Jin Air</t>
-  </si>
-  <si>
-    <t>Qingdao Airlines</t>
-  </si>
-  <si>
-    <t>Eastar Jet</t>
-  </si>
-  <si>
-    <t>Ruili Airlines</t>
-  </si>
-  <si>
-    <t>United Airlines</t>
-  </si>
-  <si>
-    <t>Scoot</t>
-  </si>
-  <si>
-    <t>SriLankan Airlines</t>
-  </si>
-  <si>
-    <t>S7 Airlines</t>
-  </si>
-  <si>
-    <t>Royal Brunei Airlines</t>
-  </si>
-  <si>
-    <t>Sichuan Airlines</t>
-  </si>
-  <si>
-    <t>Uzbekistan Airways</t>
-  </si>
-  <si>
-    <t>Spicejet</t>
-  </si>
-  <si>
-    <t>Thai Vietjet Air</t>
-  </si>
-  <si>
-    <t>Etihad Airways</t>
-  </si>
-  <si>
-    <t>T'way Air</t>
-  </si>
-  <si>
-    <t>El Al</t>
-  </si>
-  <si>
-    <t>SCAT Airlines</t>
-  </si>
-  <si>
-    <t>Citilink</t>
-  </si>
-  <si>
     <t>EXV</t>
   </si>
   <si>
-    <t>FitsAir</t>
-  </si>
-  <si>
     <t>A19N</t>
   </si>
   <si>
@@ -1263,6 +1140,132 @@
   </si>
   <si>
     <t>City, Country</t>
+  </si>
+  <si>
+    <t>JYH (9 Air)</t>
+  </si>
+  <si>
+    <t>AFA (Afcom)</t>
+  </si>
+  <si>
+    <t>AIC (Air India)</t>
+  </si>
+  <si>
+    <t>AKJ (Akasa Air)</t>
+  </si>
+  <si>
+    <t>ALK (SriLankan Airlines)</t>
+  </si>
+  <si>
+    <t>AMU (Air Macau)</t>
+  </si>
+  <si>
+    <t>AXB (Air India Express)</t>
+  </si>
+  <si>
+    <t>CEB (Cebu Pacific)</t>
+  </si>
+  <si>
+    <t>CSC (Sichuan Airlines)</t>
+  </si>
+  <si>
+    <t>CTV (Citilink)</t>
+  </si>
+  <si>
+    <t>DRK (Druk Air)</t>
+  </si>
+  <si>
+    <t>ELY (El Al)</t>
+  </si>
+  <si>
+    <t>ESR (Eastar Jet)</t>
+  </si>
+  <si>
+    <t>ETD (Etihad Airways)</t>
+  </si>
+  <si>
+    <t>EXV (FitsAir)</t>
+  </si>
+  <si>
+    <t>FFM (Firefly)</t>
+  </si>
+  <si>
+    <t>HLF (Central Airlines)</t>
+  </si>
+  <si>
+    <t>IGO (Indigo)</t>
+  </si>
+  <si>
+    <t>JDL (Jiangsu Jingdong Cargo Airlines)</t>
+  </si>
+  <si>
+    <t>JNA (Jin Air)</t>
+  </si>
+  <si>
+    <t>KMI (K-Mile Air)</t>
+  </si>
+  <si>
+    <t>KZR (Air Astana)</t>
+  </si>
+  <si>
+    <t>LHA (China Central Longhao Airlines)</t>
+  </si>
+  <si>
+    <t>MAF (MAQUARIE)</t>
+  </si>
+  <si>
+    <t>MAS (Malaysia Airlines)</t>
+  </si>
+  <si>
+    <t>MERX (Merx Aviation Servicing Limited)</t>
+  </si>
+  <si>
+    <t>MNA (Myanmar National Airlines)</t>
+  </si>
+  <si>
+    <t>NOK (NOK Air)</t>
+  </si>
+  <si>
+    <t>OKA (OK Airways)</t>
+  </si>
+  <si>
+    <t>PAL (Philippine Airlines)</t>
+  </si>
+  <si>
+    <t>Perseus (Perseus)</t>
+  </si>
+  <si>
+    <t>QDA (Qingdao Airlines)</t>
+  </si>
+  <si>
+    <t>RBA (Royal Brunei Airlines)</t>
+  </si>
+  <si>
+    <t>RLH (Ruili Airlines)</t>
+  </si>
+  <si>
+    <t>SBI (S7 Airlines)</t>
+  </si>
+  <si>
+    <t>SEJ (Spicejet)</t>
+  </si>
+  <si>
+    <t>TGW (Scoot)</t>
+  </si>
+  <si>
+    <t>TVJ (Thai Vietjet Air)</t>
+  </si>
+  <si>
+    <t>TWB (T'way Air)</t>
+  </si>
+  <si>
+    <t>UAL (United Airlines)</t>
+  </si>
+  <si>
+    <t>UZB (Uzbekistan Airways)</t>
+  </si>
+  <si>
+    <t>VSV (SCAT Airlines)</t>
   </si>
 </sst>
 </file>
@@ -1536,7 +1539,389 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="41">
+  <dxfs count="60">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="h&quot;:&quot;mm"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <name val="Roboto"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFFFFFFF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFFFFFFF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFFFFFFF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFFFFFFF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="h&quot;:&quot;mm"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="h&quot;:&quot;mm"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="d&quot;/&quot;m&quot;/&quot;yyyy&quot; &quot;"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -1545,8 +1930,62 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="2"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="2"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="2"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="2"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1569,68 +2008,8 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <color theme="2"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
+        <color theme="0"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="2"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="2"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="2"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1926,46 +2305,46 @@
   </dxfs>
   <tableStyles count="7">
     <tableStyle name="13022026-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="40"/>
-      <tableStyleElement type="headerRow" dxfId="39"/>
-      <tableStyleElement type="firstRowStripe" dxfId="38"/>
-      <tableStyleElement type="secondRowStripe" dxfId="37"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="59"/>
+      <tableStyleElement type="headerRow" dxfId="58"/>
+      <tableStyleElement type="firstRowStripe" dxfId="57"/>
+      <tableStyleElement type="secondRowStripe" dxfId="56"/>
     </tableStyle>
     <tableStyle name="_Temple-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="36"/>
-      <tableStyleElement type="headerRow" dxfId="35"/>
-      <tableStyleElement type="firstRowStripe" dxfId="34"/>
-      <tableStyleElement type="secondRowStripe" dxfId="33"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="55"/>
+      <tableStyleElement type="headerRow" dxfId="54"/>
+      <tableStyleElement type="firstRowStripe" dxfId="53"/>
+      <tableStyleElement type="secondRowStripe" dxfId="52"/>
     </tableStyle>
     <tableStyle name="_ROUTE_LIST-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="32"/>
-      <tableStyleElement type="headerRow" dxfId="31"/>
-      <tableStyleElement type="firstRowStripe" dxfId="30"/>
-      <tableStyleElement type="secondRowStripe" dxfId="29"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="51"/>
+      <tableStyleElement type="headerRow" dxfId="50"/>
+      <tableStyleElement type="firstRowStripe" dxfId="49"/>
+      <tableStyleElement type="secondRowStripe" dxfId="48"/>
     </tableStyle>
     <tableStyle name="_MAINTENANCE_STATUS-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF03000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="28"/>
-      <tableStyleElement type="headerRow" dxfId="27"/>
-      <tableStyleElement type="firstRowStripe" dxfId="26"/>
-      <tableStyleElement type="secondRowStripe" dxfId="25"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="47"/>
+      <tableStyleElement type="headerRow" dxfId="46"/>
+      <tableStyleElement type="firstRowStripe" dxfId="45"/>
+      <tableStyleElement type="secondRowStripe" dxfId="44"/>
     </tableStyle>
     <tableStyle name="_AIRLINE_LIST-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF04000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="24"/>
-      <tableStyleElement type="headerRow" dxfId="23"/>
-      <tableStyleElement type="firstRowStripe" dxfId="22"/>
-      <tableStyleElement type="secondRowStripe" dxfId="21"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="43"/>
+      <tableStyleElement type="headerRow" dxfId="42"/>
+      <tableStyleElement type="firstRowStripe" dxfId="41"/>
+      <tableStyleElement type="secondRowStripe" dxfId="40"/>
     </tableStyle>
     <tableStyle name="_AC_TYPE_LIST-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF05000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="20"/>
-      <tableStyleElement type="headerRow" dxfId="19"/>
-      <tableStyleElement type="firstRowStripe" dxfId="18"/>
-      <tableStyleElement type="secondRowStripe" dxfId="17"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="39"/>
+      <tableStyleElement type="headerRow" dxfId="38"/>
+      <tableStyleElement type="firstRowStripe" dxfId="37"/>
+      <tableStyleElement type="secondRowStripe" dxfId="36"/>
     </tableStyle>
     <tableStyle name="_STAFF-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF06000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="16"/>
-      <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="secondRowStripe" dxfId="13"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="35"/>
+      <tableStyleElement type="headerRow" dxfId="34"/>
+      <tableStyleElement type="firstRowStripe" dxfId="33"/>
+      <tableStyleElement type="secondRowStripe" dxfId="32"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1979,38 +2358,34 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="_Temple_3" displayName="_Temple_3" ref="A1:R7" headerRowDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="_Temple_3" displayName="_Temple_3" ref="A1:R7" headerRowDxfId="31" dataDxfId="0">
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="AIRLINE"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="A/C TYPE"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="REG"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="FLT NO. ARRIVAL"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="FLT NO. DEOARTURE"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="ROUTE FROM"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="ROUTE TO"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="STA Date"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="STA Time"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="STD Date"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="STD Time"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="CS"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="MECH"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="ETA Date"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="ETA Time"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="BAY"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="REMARK"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="CHECK"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="AIRLINE" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="A/C TYPE" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="REG" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="FLT NO. ARRIVAL" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="FLT NO. DEOARTURE" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="ROUTE FROM" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="ROUTE TO" dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="STA Date" dataDxfId="11"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="STA Time" dataDxfId="10"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="STD Date" dataDxfId="9"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="STD Time" dataDxfId="8"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="CS" dataDxfId="7"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="MECH" dataDxfId="6"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="ETA Date" dataDxfId="5"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="ETA Time" dataDxfId="4"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="BAY" dataDxfId="3"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="REMARK" dataDxfId="2"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="CHECK" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="13022026-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{F0C6C7A2-A8A9-4A90-8F36-DFC914407805}" name="_Temple_39" displayName="_Temple_39" ref="A1:R7" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{F0C6C7A2-A8A9-4A90-8F36-DFC914407805}" name="_Temple_39" displayName="_Temple_39" ref="A1:R7" headerRowDxfId="30">
   <tableColumns count="18">
     <tableColumn id="1" xr3:uid="{2C68D16C-7EC0-44A5-ADA5-D1F3561440F1}" name="AIRLINE"/>
     <tableColumn id="2" xr3:uid="{C0E7BE86-499E-4EA5-B397-CF909FA633DB}" name="A/C TYPE"/>
@@ -2036,9 +2411,9 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Customer_contacts" displayName="Customer_contacts" ref="A1:D27" headerRowDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Customer_contacts" displayName="Customer_contacts" ref="A1:D27" headerRowDxfId="29">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="ID" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="ID" dataDxfId="28"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Code"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Name"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="City, Country"/>
@@ -2048,9 +2423,9 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="_Maintenance_Status" displayName="_Maintenance_Status" ref="A1:B6" headerRowDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="_Maintenance_Status" displayName="_Maintenance_Status" ref="A1:B6" headerRowDxfId="27">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="ID" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="ID" dataDxfId="26"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Status"/>
   </tableColumns>
   <tableStyleInfo name="_MAINTENANCE_STATUS-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
@@ -2058,9 +2433,9 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="_Airline_list" displayName="_Airline_list" ref="A1:C43" headerRowDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="_Airline_list" displayName="_Airline_list" ref="A1:C43" headerRowDxfId="25">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="ID" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="ID" dataDxfId="24"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Code"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Airline Name"/>
   </tableColumns>
@@ -2069,9 +2444,9 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="_AC_Type_list" displayName="_AC_Type_list" ref="A1:C37" headerRowDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="_AC_Type_list" displayName="_AC_Type_list" ref="A1:C37" headerRowDxfId="23">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="ID" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="ID" dataDxfId="22"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Code"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Aircraft Name"/>
   </tableColumns>
@@ -2080,10 +2455,10 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="_Staff" displayName="_Staff" ref="A1:D131" headerRowDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="_Staff" displayName="_Staff" ref="A1:D131" headerRowDxfId="21">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="ID" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Code" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="ID" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Code" dataDxfId="19"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="Name"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="Staffs Type"/>
   </tableColumns>
@@ -2373,7 +2748,7 @@
     </row>
     <row r="2" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>260</v>
+        <v>368</v>
       </c>
       <c r="B2" s="13" t="s">
         <v>25</v>
@@ -2425,10 +2800,10 @@
     </row>
     <row r="3" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>255</v>
+        <v>371</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>272</v>
+        <v>231</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
@@ -2477,10 +2852,10 @@
     </row>
     <row r="4" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>259</v>
+        <v>371</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>273</v>
+        <v>232</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
@@ -2529,7 +2904,7 @@
     </row>
     <row r="5" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>261</v>
+        <v>373</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>25</v>
@@ -2578,10 +2953,10 @@
     </row>
     <row r="6" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B6" s="13" t="s">
         <v>234</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>275</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
@@ -2616,10 +2991,10 @@
     </row>
     <row r="7" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>232</v>
+        <v>393</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>277</v>
+        <v>236</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
@@ -2658,13 +3033,13 @@
   <dataConsolidate/>
   <phoneticPr fontId="6" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="K2:K7 O2:O7 I2:I4 I6:I7" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="K2:K7 O2:O7 I2:I4 I6:I7" xr:uid="{556E1820-0D8B-4C22-87BE-C0B169311AB4}">
       <formula1>OR(TIMEVALUE(TEXT(I2, "hh:mm:ss"))=I2, AND(ISNUMBER(I2), LEFT(CELL("format", I2))="D"))</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="H2:H7 J2:J7" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="H2:H7 J2:J7" xr:uid="{F8AD7BAB-0343-454D-8A3C-8901E956FB68}">
       <formula1>OR(NOT(ISERROR(DATEVALUE(H2))), AND(ISNUMBER(H2), LEFT(CELL("format", H2))="D"))</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="1" sqref="C2:E7 P2:Q7" xr:uid="{00000000-0002-0000-0000-000003000000}"/>
+    <dataValidation allowBlank="1" showDropDown="1" sqref="C2:E7 P2:Q7" xr:uid="{5EF31A2A-C3E7-4243-871B-AED7CED1D742}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -2672,42 +3047,36 @@
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
-        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{071DF691-626A-43F5-BBD8-41047158AB08}">
           <x14:formula1>
             <xm:f>'_MAINTENANCE_STATUS'!$B$2:$B$6</xm:f>
           </x14:formula1>
           <xm:sqref>R2:R7</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" xr:uid="{7BD3A1CD-B620-4B35-9620-E572FC6B19A5}">
+        <x14:dataValidation type="list" xr:uid="{49863A1B-748B-4998-830A-9601A1683BCA}">
           <x14:formula1>
             <xm:f>'_AC_TYPE_LIST'!$B$2:$B$37</xm:f>
           </x14:formula1>
           <xm:sqref>B2:B7</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" xr:uid="{C7B2541F-F423-43D6-8DC4-304F84BABE6C}">
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{1F962603-F644-4495-B25D-6BE423D0DB68}">
           <x14:formula1>
             <xm:f>'_AIRLINE_LIST'!$C$2:$C$43</xm:f>
           </x14:formula1>
           <xm:sqref>A2:A7</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" xr:uid="{36C3C07C-2ACD-4BD8-BB46-CC2707D0613E}">
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{4C3B29AA-E1A6-4F92-99E4-712C2F9B8471}">
           <x14:formula1>
             <xm:f>'_STAFF'!$C$2:$C$131</xm:f>
           </x14:formula1>
-          <xm:sqref>M2:M7</xm:sqref>
+          <xm:sqref>L2:M7</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" xr:uid="{F9F8BE2B-D993-4E43-9914-5414BE41B072}">
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{DE760684-B984-494D-AF51-714EF5DE3E31}">
           <x14:formula1>
             <xm:f>_ROUTE_LIST!$B$2:$B$27</xm:f>
           </x14:formula1>
           <xm:sqref>F2:G7</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" xr:uid="{0C7BD607-9FF4-4842-AE80-D7F36014CC93}">
-          <x14:formula1>
-            <xm:f>'_STAFF'!$C$2:$C$131</xm:f>
-          </x14:formula1>
-          <xm:sqref>L2:L7</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2801,7 +3170,7 @@
     </row>
     <row r="2" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>260</v>
+        <v>368</v>
       </c>
       <c r="B2" s="13" t="s">
         <v>25</v>
@@ -2853,10 +3222,10 @@
     </row>
     <row r="3" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>255</v>
+        <v>371</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>272</v>
+        <v>231</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
@@ -2905,10 +3274,10 @@
     </row>
     <row r="4" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>259</v>
+        <v>371</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>273</v>
+        <v>232</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
@@ -2957,7 +3326,7 @@
     </row>
     <row r="5" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>261</v>
+        <v>373</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>25</v>
@@ -3006,10 +3375,10 @@
     </row>
     <row r="6" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B6" s="13" t="s">
         <v>234</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>275</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
@@ -3044,10 +3413,10 @@
     </row>
     <row r="7" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>232</v>
+        <v>393</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>277</v>
+        <v>236</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
@@ -3160,7 +3529,7 @@
         <v>39</v>
       </c>
       <c r="D1" s="25" t="s">
-        <v>407</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -3174,7 +3543,7 @@
         <v>40</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>362</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -3185,10 +3554,10 @@
         <v>20</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>363</v>
+        <v>322</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>362</v>
+        <v>321</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -3202,7 +3571,7 @@
         <v>42</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>364</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -3216,7 +3585,7 @@
         <v>46</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>365</v>
+        <v>324</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -3230,7 +3599,7 @@
         <v>44</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>366</v>
+        <v>325</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -3241,10 +3610,10 @@
         <v>49</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>367</v>
+        <v>326</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>368</v>
+        <v>327</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -3258,7 +3627,7 @@
         <v>51</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>369</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -3272,7 +3641,7 @@
         <v>48</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>370</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3283,10 +3652,10 @@
         <v>211</v>
       </c>
       <c r="C10" t="s">
-        <v>371</v>
+        <v>330</v>
       </c>
       <c r="D10" t="s">
-        <v>372</v>
+        <v>331</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3297,10 +3666,10 @@
         <v>212</v>
       </c>
       <c r="C11" t="s">
-        <v>373</v>
+        <v>332</v>
       </c>
       <c r="D11" t="s">
-        <v>374</v>
+        <v>333</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3311,10 +3680,10 @@
         <v>213</v>
       </c>
       <c r="C12" t="s">
-        <v>375</v>
+        <v>334</v>
       </c>
       <c r="D12" t="s">
-        <v>376</v>
+        <v>335</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3325,10 +3694,10 @@
         <v>214</v>
       </c>
       <c r="C13" t="s">
-        <v>377</v>
+        <v>336</v>
       </c>
       <c r="D13" t="s">
-        <v>378</v>
+        <v>337</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3339,10 +3708,10 @@
         <v>215</v>
       </c>
       <c r="C14" t="s">
-        <v>379</v>
+        <v>338</v>
       </c>
       <c r="D14" t="s">
-        <v>380</v>
+        <v>339</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3353,10 +3722,10 @@
         <v>216</v>
       </c>
       <c r="C15" t="s">
-        <v>381</v>
+        <v>340</v>
       </c>
       <c r="D15" t="s">
-        <v>382</v>
+        <v>341</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3367,10 +3736,10 @@
         <v>217</v>
       </c>
       <c r="C16" t="s">
-        <v>383</v>
+        <v>342</v>
       </c>
       <c r="D16" t="s">
-        <v>384</v>
+        <v>343</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3381,10 +3750,10 @@
         <v>218</v>
       </c>
       <c r="C17" t="s">
-        <v>385</v>
+        <v>344</v>
       </c>
       <c r="D17" t="s">
-        <v>386</v>
+        <v>345</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3395,10 +3764,10 @@
         <v>219</v>
       </c>
       <c r="C18" t="s">
-        <v>387</v>
+        <v>346</v>
       </c>
       <c r="D18" t="s">
-        <v>388</v>
+        <v>347</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3409,10 +3778,10 @@
         <v>220</v>
       </c>
       <c r="C19" t="s">
-        <v>389</v>
+        <v>348</v>
       </c>
       <c r="D19" t="s">
-        <v>390</v>
+        <v>349</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3423,10 +3792,10 @@
         <v>221</v>
       </c>
       <c r="C20" t="s">
-        <v>391</v>
+        <v>350</v>
       </c>
       <c r="D20" t="s">
-        <v>392</v>
+        <v>351</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3437,10 +3806,10 @@
         <v>222</v>
       </c>
       <c r="C21" t="s">
-        <v>393</v>
+        <v>352</v>
       </c>
       <c r="D21" t="s">
-        <v>394</v>
+        <v>353</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3451,10 +3820,10 @@
         <v>223</v>
       </c>
       <c r="C22" t="s">
-        <v>395</v>
+        <v>354</v>
       </c>
       <c r="D22" t="s">
-        <v>396</v>
+        <v>355</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3465,10 +3834,10 @@
         <v>224</v>
       </c>
       <c r="C23" t="s">
-        <v>397</v>
+        <v>356</v>
       </c>
       <c r="D23" t="s">
-        <v>398</v>
+        <v>357</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3479,10 +3848,10 @@
         <v>225</v>
       </c>
       <c r="C24" t="s">
-        <v>399</v>
+        <v>358</v>
       </c>
       <c r="D24" t="s">
-        <v>400</v>
+        <v>359</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3493,10 +3862,10 @@
         <v>226</v>
       </c>
       <c r="C25" t="s">
-        <v>401</v>
+        <v>360</v>
       </c>
       <c r="D25" t="s">
-        <v>402</v>
+        <v>361</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3507,10 +3876,10 @@
         <v>227</v>
       </c>
       <c r="C26" t="s">
-        <v>403</v>
+        <v>362</v>
       </c>
       <c r="D26" t="s">
-        <v>404</v>
+        <v>363</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3521,10 +3890,10 @@
         <v>228</v>
       </c>
       <c r="C27" t="s">
-        <v>405</v>
+        <v>364</v>
       </c>
       <c r="D27" t="s">
-        <v>406</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -3651,13 +4020,13 @@
     </row>
     <row r="2" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="20">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>229</v>
+        <v>368</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -3679,13 +4048,13 @@
     </row>
     <row r="3" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="20">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>236</v>
+        <v>369</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -3707,13 +4076,13 @@
     </row>
     <row r="4" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="20">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>230</v>
+        <v>370</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -3735,13 +4104,13 @@
     </row>
     <row r="5" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="20">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>231</v>
+        <v>371</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
@@ -3763,13 +4132,13 @@
     </row>
     <row r="6" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>232</v>
+        <v>372</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
@@ -3791,13 +4160,13 @@
     </row>
     <row r="7" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>233</v>
+        <v>373</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
@@ -3819,13 +4188,13 @@
     </row>
     <row r="8" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>234</v>
+        <v>374</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
@@ -3847,13 +4216,13 @@
     </row>
     <row r="9" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="20">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>235</v>
+        <v>375</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
@@ -3875,13 +4244,13 @@
     </row>
     <row r="10" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="20">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>237</v>
+        <v>376</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
@@ -3903,13 +4272,13 @@
     </row>
     <row r="11" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="20">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>238</v>
+        <v>377</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
@@ -3931,13 +4300,13 @@
     </row>
     <row r="12" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="20">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>268</v>
+        <v>378</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
@@ -3959,13 +4328,13 @@
     </row>
     <row r="13" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="20">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>239</v>
+        <v>379</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
@@ -3987,13 +4356,13 @@
     </row>
     <row r="14" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="20">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>253</v>
+        <v>380</v>
       </c>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
@@ -4015,13 +4384,13 @@
     </row>
     <row r="15" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="20">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>86</v>
+        <v>229</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>266</v>
+        <v>381</v>
       </c>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
@@ -4043,13 +4412,13 @@
     </row>
     <row r="16" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="20">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>264</v>
+        <v>382</v>
       </c>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
@@ -4071,13 +4440,13 @@
     </row>
     <row r="17" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="20">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>240</v>
+        <v>383</v>
       </c>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
@@ -4099,13 +4468,13 @@
     </row>
     <row r="18" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="20">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>269</v>
+        <v>70</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>270</v>
+        <v>384</v>
       </c>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
@@ -4127,13 +4496,13 @@
     </row>
     <row r="19" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="20">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>241</v>
+        <v>385</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
@@ -4155,13 +4524,13 @@
     </row>
     <row r="20" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="20">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>242</v>
+        <v>386</v>
       </c>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
@@ -4183,13 +4552,13 @@
     </row>
     <row r="21" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="20">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>251</v>
+        <v>367</v>
       </c>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
@@ -4217,7 +4586,7 @@
         <v>96</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>243</v>
+        <v>387</v>
       </c>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
@@ -4239,13 +4608,13 @@
     </row>
     <row r="23" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="20">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>244</v>
+        <v>388</v>
       </c>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
@@ -4267,13 +4636,13 @@
     </row>
     <row r="24" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="20">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>245</v>
+        <v>389</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
@@ -4295,13 +4664,13 @@
     </row>
     <row r="25" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="20">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>246</v>
+        <v>390</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
@@ -4323,13 +4692,13 @@
     </row>
     <row r="26" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="20">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>247</v>
+        <v>391</v>
       </c>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
@@ -4351,13 +4720,13 @@
     </row>
     <row r="27" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="20">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>248</v>
+        <v>392</v>
       </c>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
@@ -4379,13 +4748,13 @@
     </row>
     <row r="28" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="20">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>249</v>
+        <v>393</v>
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
@@ -4407,13 +4776,13 @@
     </row>
     <row r="29" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="20">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>77</v>
+        <v>394</v>
       </c>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
@@ -4435,13 +4804,13 @@
     </row>
     <row r="30" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="20">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>250</v>
+        <v>395</v>
       </c>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
@@ -4463,13 +4832,13 @@
     </row>
     <row r="31" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="20">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>252</v>
+        <v>396</v>
       </c>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
@@ -4491,13 +4860,13 @@
     </row>
     <row r="32" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="20">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>259</v>
+        <v>397</v>
       </c>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
@@ -4519,13 +4888,13 @@
     </row>
     <row r="33" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="20">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>254</v>
+        <v>398</v>
       </c>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
@@ -4547,13 +4916,13 @@
     </row>
     <row r="34" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="20">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>258</v>
+        <v>399</v>
       </c>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
@@ -4575,13 +4944,13 @@
     </row>
     <row r="35" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="20">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>267</v>
+        <v>400</v>
       </c>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
@@ -4603,13 +4972,13 @@
     </row>
     <row r="36" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="20">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>256</v>
+        <v>401</v>
       </c>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
@@ -4631,13 +5000,13 @@
     </row>
     <row r="37" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="20">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>260</v>
+        <v>402</v>
       </c>
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
@@ -4659,13 +5028,13 @@
     </row>
     <row r="38" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="20">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>262</v>
+        <v>403</v>
       </c>
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
@@ -4687,13 +5056,13 @@
     </row>
     <row r="39" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="20">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>257</v>
+        <v>404</v>
       </c>
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
@@ -4721,7 +5090,7 @@
         <v>85</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>265</v>
+        <v>405</v>
       </c>
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
@@ -4743,13 +5112,13 @@
     </row>
     <row r="41" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="20">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>263</v>
+        <v>406</v>
       </c>
       <c r="D41" s="9"/>
       <c r="E41" s="9"/>
@@ -4771,13 +5140,13 @@
     </row>
     <row r="42" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="20">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>255</v>
+        <v>407</v>
       </c>
       <c r="D42" s="9"/>
       <c r="E42" s="9"/>
@@ -4799,13 +5168,13 @@
     </row>
     <row r="43" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="20">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="B43" s="18" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>261</v>
+        <v>408</v>
       </c>
     </row>
   </sheetData>
@@ -4859,10 +5228,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>271</v>
+        <v>230</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>271</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4881,10 +5250,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>272</v>
+        <v>231</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>272</v>
+        <v>231</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4903,10 +5272,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>273</v>
+        <v>232</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>273</v>
+        <v>232</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4914,10 +5283,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>274</v>
+        <v>233</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>274</v>
+        <v>233</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4925,10 +5294,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>275</v>
+        <v>234</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>275</v>
+        <v>234</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4936,10 +5305,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>276</v>
+        <v>235</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>276</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4947,10 +5316,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>277</v>
+        <v>236</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>277</v>
+        <v>236</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4958,10 +5327,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>278</v>
+        <v>237</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>278</v>
+        <v>237</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4969,10 +5338,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>279</v>
+        <v>238</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>279</v>
+        <v>238</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4980,10 +5349,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>280</v>
+        <v>239</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>280</v>
+        <v>239</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4991,10 +5360,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>281</v>
+        <v>240</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>281</v>
+        <v>240</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5002,10 +5371,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>282</v>
+        <v>241</v>
       </c>
       <c r="C16" t="s">
-        <v>282</v>
+        <v>241</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5013,10 +5382,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>282</v>
+        <v>241</v>
       </c>
       <c r="C17" t="s">
-        <v>282</v>
+        <v>241</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5024,10 +5393,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="C18" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5035,10 +5404,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>284</v>
+        <v>243</v>
       </c>
       <c r="C19" t="s">
-        <v>284</v>
+        <v>243</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5046,10 +5415,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>285</v>
+        <v>244</v>
       </c>
       <c r="C20" t="s">
-        <v>285</v>
+        <v>244</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5057,10 +5426,10 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>286</v>
+        <v>245</v>
       </c>
       <c r="C21" t="s">
-        <v>286</v>
+        <v>245</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5068,10 +5437,10 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>287</v>
+        <v>246</v>
       </c>
       <c r="C22" t="s">
-        <v>287</v>
+        <v>246</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5079,10 +5448,10 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>288</v>
+        <v>247</v>
       </c>
       <c r="C23" t="s">
-        <v>288</v>
+        <v>247</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5090,10 +5459,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>289</v>
+        <v>248</v>
       </c>
       <c r="C24" t="s">
-        <v>289</v>
+        <v>248</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5101,10 +5470,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>290</v>
+        <v>249</v>
       </c>
       <c r="C25" t="s">
-        <v>290</v>
+        <v>249</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5112,10 +5481,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>291</v>
+        <v>250</v>
       </c>
       <c r="C26" t="s">
-        <v>291</v>
+        <v>250</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5123,10 +5492,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>292</v>
+        <v>251</v>
       </c>
       <c r="C27" t="s">
-        <v>292</v>
+        <v>251</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5134,10 +5503,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>293</v>
+        <v>252</v>
       </c>
       <c r="C28" t="s">
-        <v>293</v>
+        <v>252</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5145,10 +5514,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>294</v>
+        <v>253</v>
       </c>
       <c r="C29" t="s">
-        <v>294</v>
+        <v>253</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5167,10 +5536,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>295</v>
+        <v>254</v>
       </c>
       <c r="C31" t="s">
-        <v>295</v>
+        <v>254</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5178,10 +5547,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>296</v>
+        <v>255</v>
       </c>
       <c r="C32" t="s">
-        <v>296</v>
+        <v>255</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5189,10 +5558,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>297</v>
+        <v>256</v>
       </c>
       <c r="C33" t="s">
-        <v>297</v>
+        <v>256</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5200,10 +5569,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="C34" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5211,10 +5580,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>299</v>
+        <v>258</v>
       </c>
       <c r="C35" t="s">
-        <v>299</v>
+        <v>258</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5222,10 +5591,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>300</v>
+        <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>300</v>
+        <v>259</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5289,7 +5658,7 @@
         <v>34</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>301</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5303,7 +5672,7 @@
         <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5317,7 +5686,7 @@
         <v>27</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5331,7 +5700,7 @@
         <v>102</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>303</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5345,7 +5714,7 @@
         <v>103</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>304</v>
+        <v>263</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5359,7 +5728,7 @@
         <v>30</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>305</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5370,10 +5739,10 @@
         <v>67</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>306</v>
+        <v>265</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>307</v>
+        <v>266</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5387,7 +5756,7 @@
         <v>104</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>304</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5401,7 +5770,7 @@
         <v>105</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>308</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5415,7 +5784,7 @@
         <v>106</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>309</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5426,10 +5795,10 @@
         <v>72</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>310</v>
+        <v>269</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>311</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5443,7 +5812,7 @@
         <v>107</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>309</v>
+        <v>268</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5457,7 +5826,7 @@
         <v>108</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>304</v>
+        <v>263</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5471,7 +5840,7 @@
         <v>109</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5482,10 +5851,10 @@
         <v>66</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>312</v>
+        <v>271</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>313</v>
+        <v>272</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5499,7 +5868,7 @@
         <v>110</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5513,7 +5882,7 @@
         <v>111</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>313</v>
+        <v>272</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5527,7 +5896,7 @@
         <v>112</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>314</v>
+        <v>273</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5541,7 +5910,7 @@
         <v>113</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>315</v>
+        <v>274</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5555,7 +5924,7 @@
         <v>114</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5569,7 +5938,7 @@
         <v>115</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>316</v>
+        <v>275</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5583,7 +5952,7 @@
         <v>116</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>317</v>
+        <v>276</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5597,7 +5966,7 @@
         <v>117</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>309</v>
+        <v>268</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5611,7 +5980,7 @@
         <v>118</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5625,7 +5994,7 @@
         <v>119</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>304</v>
+        <v>263</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5639,7 +6008,7 @@
         <v>120</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>318</v>
+        <v>277</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5653,7 +6022,7 @@
         <v>121</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5664,10 +6033,10 @@
         <v>35</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>319</v>
+        <v>278</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>320</v>
+        <v>279</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5681,7 +6050,7 @@
         <v>122</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>321</v>
+        <v>280</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5695,7 +6064,7 @@
         <v>123</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5709,7 +6078,7 @@
         <v>124</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>322</v>
+        <v>281</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5723,7 +6092,7 @@
         <v>125</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>309</v>
+        <v>268</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5737,7 +6106,7 @@
         <v>126</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>313</v>
+        <v>272</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5751,7 +6120,7 @@
         <v>127</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>309</v>
+        <v>268</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5765,7 +6134,7 @@
         <v>128</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>309</v>
+        <v>268</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5779,7 +6148,7 @@
         <v>129</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>323</v>
+        <v>282</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5793,7 +6162,7 @@
         <v>130</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>313</v>
+        <v>272</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5807,7 +6176,7 @@
         <v>131</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5821,7 +6190,7 @@
         <v>132</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5835,7 +6204,7 @@
         <v>133</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>323</v>
+        <v>282</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5849,7 +6218,7 @@
         <v>134</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>313</v>
+        <v>272</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5860,10 +6229,10 @@
         <v>45</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>324</v>
+        <v>283</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>325</v>
+        <v>284</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5877,7 +6246,7 @@
         <v>135</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5888,10 +6257,10 @@
         <v>57</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>326</v>
+        <v>285</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>327</v>
+        <v>286</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5905,7 +6274,7 @@
         <v>136</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>328</v>
+        <v>287</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5919,7 +6288,7 @@
         <v>137</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>329</v>
+        <v>288</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5933,7 +6302,7 @@
         <v>138</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>304</v>
+        <v>263</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5947,7 +6316,7 @@
         <v>139</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>309</v>
+        <v>268</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5961,7 +6330,7 @@
         <v>140</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>330</v>
+        <v>289</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5975,7 +6344,7 @@
         <v>141</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>331</v>
+        <v>290</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5989,7 +6358,7 @@
         <v>142</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>309</v>
+        <v>268</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6003,7 +6372,7 @@
         <v>143</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>315</v>
+        <v>274</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6017,7 +6386,7 @@
         <v>144</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>309</v>
+        <v>268</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6031,7 +6400,7 @@
         <v>145</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>305</v>
+        <v>264</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6045,7 +6414,7 @@
         <v>146</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6059,7 +6428,7 @@
         <v>147</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>309</v>
+        <v>268</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6073,7 +6442,7 @@
         <v>148</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>332</v>
+        <v>291</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6084,10 +6453,10 @@
         <v>36</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>333</v>
+        <v>292</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>334</v>
+        <v>293</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6098,10 +6467,10 @@
         <v>56</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>335</v>
+        <v>294</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6115,7 +6484,7 @@
         <v>149</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>304</v>
+        <v>263</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6126,10 +6495,10 @@
         <v>48</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>336</v>
+        <v>295</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>337</v>
+        <v>296</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6143,7 +6512,7 @@
         <v>150</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6157,7 +6526,7 @@
         <v>151</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>309</v>
+        <v>268</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6171,7 +6540,7 @@
         <v>152</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>309</v>
+        <v>268</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6185,7 +6554,7 @@
         <v>153</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>304</v>
+        <v>263</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6199,7 +6568,7 @@
         <v>154</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>309</v>
+        <v>268</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6213,7 +6582,7 @@
         <v>155</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6227,7 +6596,7 @@
         <v>156</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6238,10 +6607,10 @@
         <v>44</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>338</v>
+        <v>297</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>339</v>
+        <v>298</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6255,7 +6624,7 @@
         <v>157</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>340</v>
+        <v>299</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6269,7 +6638,7 @@
         <v>158</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>341</v>
+        <v>300</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6283,7 +6652,7 @@
         <v>159</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>342</v>
+        <v>301</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6297,7 +6666,7 @@
         <v>160</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>304</v>
+        <v>263</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6311,7 +6680,7 @@
         <v>161</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6325,7 +6694,7 @@
         <v>162</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6339,7 +6708,7 @@
         <v>163</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>343</v>
+        <v>302</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6353,7 +6722,7 @@
         <v>164</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6367,7 +6736,7 @@
         <v>165</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6381,7 +6750,7 @@
         <v>166</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6395,7 +6764,7 @@
         <v>167</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6409,7 +6778,7 @@
         <v>168</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6423,7 +6792,7 @@
         <v>169</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>309</v>
+        <v>268</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6437,7 +6806,7 @@
         <v>170</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6448,10 +6817,10 @@
         <v>43</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>344</v>
+        <v>303</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>345</v>
+        <v>304</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6465,7 +6834,7 @@
         <v>171</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6479,7 +6848,7 @@
         <v>172</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6493,7 +6862,7 @@
         <v>173</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6507,7 +6876,7 @@
         <v>174</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>309</v>
+        <v>268</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6521,7 +6890,7 @@
         <v>175</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>309</v>
+        <v>268</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6535,7 +6904,7 @@
         <v>176</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>304</v>
+        <v>263</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6549,7 +6918,7 @@
         <v>177</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>346</v>
+        <v>305</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6563,7 +6932,7 @@
         <v>178</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>309</v>
+        <v>268</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6577,7 +6946,7 @@
         <v>179</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>330</v>
+        <v>289</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6591,7 +6960,7 @@
         <v>180</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>309</v>
+        <v>268</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6605,7 +6974,7 @@
         <v>181</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>307</v>
+        <v>266</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6619,7 +6988,7 @@
         <v>182</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6630,10 +6999,10 @@
         <v>31</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>347</v>
+        <v>306</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>348</v>
+        <v>307</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6647,7 +7016,7 @@
         <v>183</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6661,7 +7030,7 @@
         <v>184</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>304</v>
+        <v>263</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6675,7 +7044,7 @@
         <v>185</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>349</v>
+        <v>308</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6689,7 +7058,7 @@
         <v>186</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>304</v>
+        <v>263</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6700,10 +7069,10 @@
         <v>166</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>350</v>
+        <v>309</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>351</v>
+        <v>310</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6717,7 +7086,7 @@
         <v>187</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>352</v>
+        <v>311</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6731,7 +7100,7 @@
         <v>188</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>309</v>
+        <v>268</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6745,7 +7114,7 @@
         <v>189</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>304</v>
+        <v>263</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6759,7 +7128,7 @@
         <v>190</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>351</v>
+        <v>310</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6773,7 +7142,7 @@
         <v>191</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6787,7 +7156,7 @@
         <v>192</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>304</v>
+        <v>263</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6801,7 +7170,7 @@
         <v>193</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>309</v>
+        <v>268</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6815,7 +7184,7 @@
         <v>194</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6826,10 +7195,10 @@
         <v>141</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>353</v>
+        <v>312</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6843,7 +7212,7 @@
         <v>195</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>304</v>
+        <v>263</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6857,7 +7226,7 @@
         <v>196</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>309</v>
+        <v>268</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6868,10 +7237,10 @@
         <v>49</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>354</v>
+        <v>313</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6885,7 +7254,7 @@
         <v>197</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>309</v>
+        <v>268</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6899,7 +7268,7 @@
         <v>198</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6913,7 +7282,7 @@
         <v>199</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>311</v>
+        <v>270</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -6927,7 +7296,7 @@
         <v>200</v>
       </c>
       <c r="D119" t="s">
-        <v>355</v>
+        <v>314</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -6941,7 +7310,7 @@
         <v>201</v>
       </c>
       <c r="D120" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -6955,7 +7324,7 @@
         <v>202</v>
       </c>
       <c r="D121" t="s">
-        <v>315</v>
+        <v>274</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -6969,7 +7338,7 @@
         <v>203</v>
       </c>
       <c r="D122" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -6980,10 +7349,10 @@
         <v>30</v>
       </c>
       <c r="C123" t="s">
-        <v>356</v>
+        <v>315</v>
       </c>
       <c r="D123" t="s">
-        <v>357</v>
+        <v>316</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -6997,7 +7366,7 @@
         <v>204</v>
       </c>
       <c r="D124" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -7008,10 +7377,10 @@
         <v>46</v>
       </c>
       <c r="C125" t="s">
-        <v>358</v>
+        <v>317</v>
       </c>
       <c r="D125" t="s">
-        <v>351</v>
+        <v>310</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -7025,7 +7394,7 @@
         <v>205</v>
       </c>
       <c r="D126" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -7039,7 +7408,7 @@
         <v>206</v>
       </c>
       <c r="D127" t="s">
-        <v>359</v>
+        <v>318</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -7053,7 +7422,7 @@
         <v>207</v>
       </c>
       <c r="D128" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -7067,7 +7436,7 @@
         <v>208</v>
       </c>
       <c r="D129" t="s">
-        <v>360</v>
+        <v>319</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -7081,7 +7450,7 @@
         <v>209</v>
       </c>
       <c r="D130" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -7095,7 +7464,7 @@
         <v>210</v>
       </c>
       <c r="D131" t="s">
-        <v>361</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>

--- a/public/flie/Template Aircraft Sched-Mapping.xlsx
+++ b/public/flie/Template Aircraft Sched-Mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e55ca4bad86d753/Desktop/Images/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="253" documentId="11_C026B8655C66716B89AF53C5EB1F5D9AB1CC498E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77E9AAF8-E90A-437E-8311-1633E45149C9}"/>
+  <xr:revisionPtr revIDLastSave="301" documentId="11_C026B8655C66716B89AF53C5EB1F5D9AB1CC498E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A066D6EF-E6B5-4A65-A48C-7E749AD42CDA}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="854" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,9 +17,10 @@
     <sheet name="_Temple" sheetId="2" r:id="rId2"/>
     <sheet name="_ROUTE_LIST" sheetId="3" r:id="rId3"/>
     <sheet name="_MAINTENANCE_STATUS" sheetId="4" r:id="rId4"/>
-    <sheet name="_AIRLINE_LIST" sheetId="5" r:id="rId5"/>
-    <sheet name="_AC_TYPE_LIST" sheetId="6" r:id="rId6"/>
-    <sheet name="_STAFF" sheetId="7" r:id="rId7"/>
+    <sheet name="_STATION_LIST" sheetId="8" r:id="rId5"/>
+    <sheet name="_AIRLINE_LIST" sheetId="5" r:id="rId6"/>
+    <sheet name="_AC_TYPE_LIST" sheetId="6" r:id="rId7"/>
+    <sheet name="_STAFF" sheetId="7" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="419">
   <si>
     <t>AIRLINE</t>
   </si>
@@ -1266,6 +1267,36 @@
   </si>
   <si>
     <t>VSV (SCAT Airlines)</t>
+  </si>
+  <si>
+    <t>STATION</t>
+  </si>
+  <si>
+    <t>BKK (Suvarnabhumi Airport)</t>
+  </si>
+  <si>
+    <t>DMK (Don Mueang Airport)</t>
+  </si>
+  <si>
+    <t>HKT (Phuket International Airport)</t>
+  </si>
+  <si>
+    <t>HDY (Hat Yai International Airport)</t>
+  </si>
+  <si>
+    <t>CNX (Chiang Mai International Airport)</t>
+  </si>
+  <si>
+    <t>CEI (Mae Fah Luang - Chiang Rai International Airport)</t>
+  </si>
+  <si>
+    <t>UTH (Udon Thani International Airport)</t>
+  </si>
+  <si>
+    <t>KBV (Krabi International Airport)</t>
+  </si>
+  <si>
+    <t>Station Name</t>
   </si>
 </sst>
 </file>
@@ -1539,7 +1570,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="60">
+  <dxfs count="83">
     <dxf>
       <font>
         <b val="0"/>
@@ -1557,6 +1588,106 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="2"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="2"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="2"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="2"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="2"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="2"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -1917,88 +2048,22 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
         <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <color theme="2"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="2"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="2"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="2"/>
+        <color theme="1"/>
         <name val="Arial"/>
         <scheme val="minor"/>
       </font>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="2"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2010,6 +2075,400 @@
         <sz val="10"/>
         <color theme="0"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="h&quot;:&quot;mm"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <name val="Roboto"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFFFFFFF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFFFFFFF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFFFFFFF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFFFFFFF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="h&quot;:&quot;mm"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="h&quot;:&quot;mm"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="d&quot;/&quot;m&quot;/&quot;yyyy&quot; &quot;"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2305,46 +2764,46 @@
   </dxfs>
   <tableStyles count="7">
     <tableStyle name="13022026-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="59"/>
-      <tableStyleElement type="headerRow" dxfId="58"/>
-      <tableStyleElement type="firstRowStripe" dxfId="57"/>
-      <tableStyleElement type="secondRowStripe" dxfId="56"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="82"/>
+      <tableStyleElement type="headerRow" dxfId="81"/>
+      <tableStyleElement type="firstRowStripe" dxfId="80"/>
+      <tableStyleElement type="secondRowStripe" dxfId="79"/>
     </tableStyle>
     <tableStyle name="_Temple-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="55"/>
-      <tableStyleElement type="headerRow" dxfId="54"/>
-      <tableStyleElement type="firstRowStripe" dxfId="53"/>
-      <tableStyleElement type="secondRowStripe" dxfId="52"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="78"/>
+      <tableStyleElement type="headerRow" dxfId="77"/>
+      <tableStyleElement type="firstRowStripe" dxfId="76"/>
+      <tableStyleElement type="secondRowStripe" dxfId="75"/>
     </tableStyle>
     <tableStyle name="_ROUTE_LIST-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="51"/>
-      <tableStyleElement type="headerRow" dxfId="50"/>
-      <tableStyleElement type="firstRowStripe" dxfId="49"/>
-      <tableStyleElement type="secondRowStripe" dxfId="48"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="74"/>
+      <tableStyleElement type="headerRow" dxfId="73"/>
+      <tableStyleElement type="firstRowStripe" dxfId="72"/>
+      <tableStyleElement type="secondRowStripe" dxfId="71"/>
     </tableStyle>
     <tableStyle name="_MAINTENANCE_STATUS-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF03000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="47"/>
-      <tableStyleElement type="headerRow" dxfId="46"/>
-      <tableStyleElement type="firstRowStripe" dxfId="45"/>
-      <tableStyleElement type="secondRowStripe" dxfId="44"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="70"/>
+      <tableStyleElement type="headerRow" dxfId="69"/>
+      <tableStyleElement type="firstRowStripe" dxfId="68"/>
+      <tableStyleElement type="secondRowStripe" dxfId="67"/>
     </tableStyle>
     <tableStyle name="_AIRLINE_LIST-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF04000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="43"/>
-      <tableStyleElement type="headerRow" dxfId="42"/>
-      <tableStyleElement type="firstRowStripe" dxfId="41"/>
-      <tableStyleElement type="secondRowStripe" dxfId="40"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="66"/>
+      <tableStyleElement type="headerRow" dxfId="65"/>
+      <tableStyleElement type="firstRowStripe" dxfId="64"/>
+      <tableStyleElement type="secondRowStripe" dxfId="63"/>
     </tableStyle>
     <tableStyle name="_AC_TYPE_LIST-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF05000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="39"/>
-      <tableStyleElement type="headerRow" dxfId="38"/>
-      <tableStyleElement type="firstRowStripe" dxfId="37"/>
-      <tableStyleElement type="secondRowStripe" dxfId="36"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="62"/>
+      <tableStyleElement type="headerRow" dxfId="61"/>
+      <tableStyleElement type="firstRowStripe" dxfId="60"/>
+      <tableStyleElement type="secondRowStripe" dxfId="59"/>
     </tableStyle>
     <tableStyle name="_STAFF-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF06000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="35"/>
-      <tableStyleElement type="headerRow" dxfId="34"/>
-      <tableStyleElement type="firstRowStripe" dxfId="33"/>
-      <tableStyleElement type="secondRowStripe" dxfId="32"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="58"/>
+      <tableStyleElement type="headerRow" dxfId="57"/>
+      <tableStyleElement type="firstRowStripe" dxfId="56"/>
+      <tableStyleElement type="secondRowStripe" dxfId="55"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -2358,62 +2817,68 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="_Temple_3" displayName="_Temple_3" ref="A1:R7" headerRowDxfId="31" dataDxfId="0">
-  <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="AIRLINE" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="A/C TYPE" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="REG" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="FLT NO. ARRIVAL" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="FLT NO. DEOARTURE" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="ROUTE FROM" dataDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="ROUTE TO" dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="STA Date" dataDxfId="11"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="STA Time" dataDxfId="10"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="STD Date" dataDxfId="9"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="STD Time" dataDxfId="8"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="CS" dataDxfId="7"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="MECH" dataDxfId="6"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="ETA Date" dataDxfId="5"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="ETA Time" dataDxfId="4"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="BAY" dataDxfId="3"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="REMARK" dataDxfId="2"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="CHECK" dataDxfId="1"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="_Temple_3" displayName="_Temple_3" ref="A1:S7" headerRowDxfId="54" dataDxfId="53">
+  <tableColumns count="19">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="AIRLINE" dataDxfId="52"/>
+    <tableColumn id="19" xr3:uid="{BAF6AC46-6F28-4C77-8BEB-F4AF48C56BDA}" name="STATION" dataDxfId="51"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="A/C TYPE" dataDxfId="50"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="REG" dataDxfId="49"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="FLT NO. ARRIVAL" dataDxfId="48"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="FLT NO. DEOARTURE" dataDxfId="47"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="ROUTE FROM" dataDxfId="46"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="ROUTE TO" dataDxfId="45"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="STA Date" dataDxfId="44"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="STA Time" dataDxfId="43"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="STD Date" dataDxfId="42"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="STD Time" dataDxfId="41"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="CS" dataDxfId="40"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="MECH" dataDxfId="39"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="ETA Date" dataDxfId="38"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="ETA Time" dataDxfId="37"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="BAY" dataDxfId="36"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="REMARK" dataDxfId="35"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="CHECK" dataDxfId="34"/>
   </tableColumns>
   <tableStyleInfo name="13022026-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{F0C6C7A2-A8A9-4A90-8F36-DFC914407805}" name="_Temple_39" displayName="_Temple_39" ref="A1:R7" headerRowDxfId="30">
-  <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{2C68D16C-7EC0-44A5-ADA5-D1F3561440F1}" name="AIRLINE"/>
-    <tableColumn id="2" xr3:uid="{C0E7BE86-499E-4EA5-B397-CF909FA633DB}" name="A/C TYPE"/>
-    <tableColumn id="3" xr3:uid="{65E04683-8DDB-4BC0-928B-F60F2515204E}" name="REG"/>
-    <tableColumn id="4" xr3:uid="{F68ABC82-B003-491B-BE84-B39AB87C2990}" name="FLT NO. ARRIVAL"/>
-    <tableColumn id="5" xr3:uid="{C14218E8-3183-4110-9016-2AC26CACC631}" name="FLT NO. DEOARTURE"/>
-    <tableColumn id="6" xr3:uid="{2B002552-8A2C-4AE9-87A4-617BD99840C2}" name="ROUTE FROM"/>
-    <tableColumn id="7" xr3:uid="{F90B353D-4ED1-4F6D-BA74-1CA655408B08}" name="ROUTE TO"/>
-    <tableColumn id="8" xr3:uid="{815EC1C5-C818-4653-A360-AEEDADBF0E65}" name="STA Date"/>
-    <tableColumn id="9" xr3:uid="{FE83D46C-0121-4AC9-AD27-F0C7193326AB}" name="STA Time"/>
-    <tableColumn id="10" xr3:uid="{E7985EFB-41F8-47D0-BAEC-BD23330E8883}" name="STD Date"/>
-    <tableColumn id="11" xr3:uid="{5BA4ACD7-5ED5-48BB-8236-5242C4282448}" name="STD Time"/>
-    <tableColumn id="12" xr3:uid="{7488BD7E-1A46-4A92-A629-A7C88A2724B2}" name="CS"/>
-    <tableColumn id="13" xr3:uid="{C033B3F3-B37F-49F9-BE7A-4A945B42F577}" name="MECH"/>
-    <tableColumn id="14" xr3:uid="{C5704CFC-8C92-433C-9517-F687405FA49F}" name="ETA Date"/>
-    <tableColumn id="15" xr3:uid="{0E13C4EF-4BD7-4C6C-A135-4DB86E7267EA}" name="ETA Time"/>
-    <tableColumn id="16" xr3:uid="{8F12CB51-AD0B-494B-8A26-1D04354529E2}" name="BAY"/>
-    <tableColumn id="17" xr3:uid="{B780B636-133D-464D-A41E-BEE9148BFEF2}" name="REMARK"/>
-    <tableColumn id="18" xr3:uid="{8389347F-3AA3-45CA-B232-EA2415C74C68}" name="CHECK"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{48DFF803-911B-4FE3-BB46-611E436C6E66}" name="_Temple_310" displayName="_Temple_310" ref="A1:S7" headerRowDxfId="33" dataDxfId="32">
+  <tableColumns count="19">
+    <tableColumn id="1" xr3:uid="{1A6F35CD-0F9F-41C2-B8C5-FD0A379F3623}" name="AIRLINE" dataDxfId="31"/>
+    <tableColumn id="19" xr3:uid="{E087F79A-673C-479F-BF88-41812CEA8D42}" name="STATION" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{583712A2-26FC-49F8-96E6-400B46FF5893}" name="A/C TYPE" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{09D779AA-842B-43BC-BFDF-291735E3C9FE}" name="REG" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{CE1AAB2C-95E0-4911-B892-43B0493D6CE2}" name="FLT NO. ARRIVAL" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{DE13C7C2-472D-4F7E-8F2C-6B1D034B7371}" name="FLT NO. DEOARTURE" dataDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{39FF2C83-4BEC-4361-B61D-931CFFD452A9}" name="ROUTE FROM" dataDxfId="26"/>
+    <tableColumn id="7" xr3:uid="{DCAF0059-9663-47BA-B597-CA7029EEFCDB}" name="ROUTE TO" dataDxfId="25"/>
+    <tableColumn id="8" xr3:uid="{3CACA6E5-9C73-4E2B-A3F3-C954A293155E}" name="STA Date" dataDxfId="24"/>
+    <tableColumn id="9" xr3:uid="{FC2248DE-06C5-4873-B5B1-A3583E433456}" name="STA Time" dataDxfId="23"/>
+    <tableColumn id="10" xr3:uid="{BF9CEFAA-D7C6-4CE0-A028-F3383A388DE2}" name="STD Date" dataDxfId="22"/>
+    <tableColumn id="11" xr3:uid="{ED1B8278-4020-4204-98AF-0991CADD94C7}" name="STD Time" dataDxfId="21"/>
+    <tableColumn id="12" xr3:uid="{2634097F-C0F7-4718-8B65-F46D76DE7F20}" name="CS" dataDxfId="20"/>
+    <tableColumn id="13" xr3:uid="{8DE7FF21-5E5D-4909-BA98-386ED250A6D0}" name="MECH" dataDxfId="19"/>
+    <tableColumn id="14" xr3:uid="{AB5F5E9E-FAF2-4100-984D-24C5F2530A9E}" name="ETA Date" dataDxfId="18"/>
+    <tableColumn id="15" xr3:uid="{BEC2F91D-1D31-441C-B07B-9FBE48E2496E}" name="ETA Time" dataDxfId="17"/>
+    <tableColumn id="16" xr3:uid="{C10941E3-F4EE-42D5-A3EB-3A131A5FA467}" name="BAY" dataDxfId="16"/>
+    <tableColumn id="17" xr3:uid="{13D34A03-D50A-4A95-9802-AA8F5AF32F39}" name="REMARK" dataDxfId="15"/>
+    <tableColumn id="18" xr3:uid="{6D5836A2-833A-40DC-AD27-FB56B7429611}" name="CHECK" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="13022026-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Customer_contacts" displayName="Customer_contacts" ref="A1:D27" headerRowDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Customer_contacts" displayName="Customer_contacts" ref="A1:D27" headerRowDxfId="13">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="ID" dataDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="ID" dataDxfId="12"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Code"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Name"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="City, Country"/>
@@ -2423,9 +2888,9 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="_Maintenance_Status" displayName="_Maintenance_Status" ref="A1:B6" headerRowDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="_Maintenance_Status" displayName="_Maintenance_Status" ref="A1:B6" headerRowDxfId="11">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="ID" dataDxfId="26"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="ID" dataDxfId="10"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Status"/>
   </tableColumns>
   <tableStyleInfo name="_MAINTENANCE_STATUS-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
@@ -2433,9 +2898,20 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="_Airline_list" displayName="_Airline_list" ref="A1:C43" headerRowDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4907D024-0C33-4AF0-9BE7-C3DC0561F570}" name="_Airline_list3" displayName="_Airline_list3" ref="A1:C9" headerRowDxfId="9">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="ID" dataDxfId="24"/>
+    <tableColumn id="1" xr3:uid="{73F5F97F-2E47-44E5-A1BB-2F0B15DF8D7C}" name="ID" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{2A28DCBD-63FB-47D3-A974-5B1BCED7275F}" name="Code"/>
+    <tableColumn id="3" xr3:uid="{18CD38F9-41BF-4EB0-8B6D-DD8E8D6A760D}" name="Station Name"/>
+  </tableColumns>
+  <tableStyleInfo name="_AIRLINE_LIST-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="_Airline_list" displayName="_Airline_list" ref="A1:C43" headerRowDxfId="7">
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="ID" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Code"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Airline Name"/>
   </tableColumns>
@@ -2443,10 +2919,10 @@
 </table>
 </file>
 
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="_AC_Type_list" displayName="_AC_Type_list" ref="A1:C37" headerRowDxfId="23">
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="_AC_Type_list" displayName="_AC_Type_list" ref="A1:C37" headerRowDxfId="5">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="ID" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="ID" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Code"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Aircraft Name"/>
   </tableColumns>
@@ -2454,11 +2930,11 @@
 </table>
 </file>
 
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="_Staff" displayName="_Staff" ref="A1:D131" headerRowDxfId="21">
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="_Staff" displayName="_Staff" ref="A1:D131" headerRowDxfId="3">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="ID" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Code" dataDxfId="19"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="ID" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Code" dataDxfId="1"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="Name"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="Staffs Type"/>
   </tableColumns>
@@ -2667,11 +3143,461 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.73046875" customWidth="1"/>
-    <col min="2" max="2" width="33.1328125" customWidth="1"/>
+    <col min="1" max="1" width="27.86328125" customWidth="1"/>
+    <col min="2" max="2" width="17.9296875" customWidth="1"/>
+    <col min="3" max="3" width="33.1328125" customWidth="1"/>
+    <col min="4" max="4" width="19.59765625" customWidth="1"/>
+    <col min="5" max="5" width="26.265625" customWidth="1"/>
+    <col min="6" max="6" width="25.86328125" customWidth="1"/>
+    <col min="7" max="7" width="18.86328125" customWidth="1"/>
+    <col min="8" max="8" width="17.59765625" customWidth="1"/>
+    <col min="9" max="9" width="15.59765625" customWidth="1"/>
+    <col min="10" max="10" width="14.73046875" customWidth="1"/>
+    <col min="11" max="11" width="15.59765625" customWidth="1"/>
+    <col min="12" max="12" width="12.59765625" customWidth="1"/>
+    <col min="13" max="13" width="33.86328125" customWidth="1"/>
+    <col min="14" max="14" width="33.3984375" customWidth="1"/>
+    <col min="15" max="15" width="12.3984375" customWidth="1"/>
+    <col min="16" max="16" width="17.59765625" customWidth="1"/>
+    <col min="17" max="17" width="15.1328125" customWidth="1"/>
+    <col min="18" max="18" width="15.3984375" customWidth="1"/>
+    <col min="19" max="19" width="15.1328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>409</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I2" s="3">
+        <v>46092</v>
+      </c>
+      <c r="J2" s="4">
+        <v>0.5625</v>
+      </c>
+      <c r="K2" s="5">
+        <v>46092</v>
+      </c>
+      <c r="L2" s="4">
+        <v>0.61805555555555558</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" s="6">
+        <v>46092</v>
+      </c>
+      <c r="P2" s="4">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I3" s="3">
+        <v>46093</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="K3" s="5">
+        <v>46093</v>
+      </c>
+      <c r="L3" s="4">
+        <v>0.65972222222222221</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="O3" s="7">
+        <v>46093</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.59722222222222221</v>
+      </c>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="3">
+        <v>46094</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="K4" s="5">
+        <v>46094</v>
+      </c>
+      <c r="L4" s="4">
+        <v>0.70138888888888884</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="O4" s="6">
+        <v>46094</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.63888888888888884</v>
+      </c>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I5" s="3">
+        <v>46095</v>
+      </c>
+      <c r="K5" s="5">
+        <v>46095</v>
+      </c>
+      <c r="L5" s="4">
+        <v>0.74305555555555558</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O5" s="7">
+        <v>46095</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.68055555555555558</v>
+      </c>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="3">
+        <v>46096</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.6875</v>
+      </c>
+      <c r="K6" s="5">
+        <v>46096</v>
+      </c>
+      <c r="L6" s="4"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="6">
+        <v>46096</v>
+      </c>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="3">
+        <v>46097</v>
+      </c>
+      <c r="J7" s="4"/>
+      <c r="K7" s="5">
+        <v>46097</v>
+      </c>
+      <c r="L7" s="4"/>
+      <c r="M7" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O7" s="8">
+        <v>46097</v>
+      </c>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataConsolidate/>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <dataValidations count="3">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="L2:L7 P2:P7 J2:J4 J6:J7" xr:uid="{556E1820-0D8B-4C22-87BE-C0B169311AB4}">
+      <formula1>OR(TIMEVALUE(TEXT(J2, "hh:mm:ss"))=J2, AND(ISNUMBER(J2), LEFT(CELL("format", J2))="D"))</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="I2:I7 K2:K7" xr:uid="{F8AD7BAB-0343-454D-8A3C-8901E956FB68}">
+      <formula1>OR(NOT(ISERROR(DATEVALUE(I2))), AND(ISNUMBER(I2), LEFT(CELL("format", I2))="D"))</formula1>
+    </dataValidation>
+    <dataValidation allowBlank="1" showDropDown="1" sqref="D2:F7 Q2:R7" xr:uid="{5EF31A2A-C3E7-4243-871B-AED7CED1D742}"/>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{071DF691-626A-43F5-BBD8-41047158AB08}">
+          <x14:formula1>
+            <xm:f>'_MAINTENANCE_STATUS'!$B$2:$B$6</xm:f>
+          </x14:formula1>
+          <xm:sqref>S2:S7</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" xr:uid="{49863A1B-748B-4998-830A-9601A1683BCA}">
+          <x14:formula1>
+            <xm:f>'_AC_TYPE_LIST'!$B$2:$B$37</xm:f>
+          </x14:formula1>
+          <xm:sqref>C2:C7</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{1F962603-F644-4495-B25D-6BE423D0DB68}">
+          <x14:formula1>
+            <xm:f>'_AIRLINE_LIST'!$C$2:$C$43</xm:f>
+          </x14:formula1>
+          <xm:sqref>A2:A7</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{4C3B29AA-E1A6-4F92-99E4-712C2F9B8471}">
+          <x14:formula1>
+            <xm:f>'_STAFF'!$C$2:$C$131</xm:f>
+          </x14:formula1>
+          <xm:sqref>M2:N7</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{DE760684-B984-494D-AF51-714EF5DE3E31}">
+          <x14:formula1>
+            <xm:f>_ROUTE_LIST!$B$2:$B$27</xm:f>
+          </x14:formula1>
+          <xm:sqref>G2:H7</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{AD446309-8BCD-47BB-B3F5-89B64550FA49}">
+          <x14:formula1>
+            <xm:f>_STATION_LIST!$B$2:$B$9</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B7</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:S7"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="27.86328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.1328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.59765625" customWidth="1"/>
     <col min="4" max="4" width="26.265625" customWidth="1"/>
     <col min="5" max="5" width="25.86328125" customWidth="1"/>
@@ -2690,356 +3616,375 @@
     <col min="18" max="18" width="15.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="15" t="s">
+        <v>409</v>
+      </c>
+      <c r="C1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="D1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="E1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="F1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="G1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="H1" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="I1" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="J1" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="K1" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="15" t="s">
+      <c r="L1" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="15" t="s">
+      <c r="M1" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="15" t="s">
+      <c r="N1" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="17" t="s">
+      <c r="O1" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="15" t="s">
+      <c r="P1" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="15" t="s">
+      <c r="Q1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="15" t="s">
+      <c r="R1" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="15" t="s">
+      <c r="S1" s="15" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="2"/>
+      <c r="E2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I2" s="3">
         <v>46092</v>
       </c>
-      <c r="I2" s="4">
+      <c r="J2" s="4">
         <v>0.5625</v>
       </c>
-      <c r="J2" s="5">
+      <c r="K2" s="5">
         <v>46092</v>
       </c>
-      <c r="K2" s="4">
+      <c r="L2" s="4">
         <v>0.61805555555555558</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="6">
+      <c r="N2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" s="6">
         <v>46092</v>
       </c>
-      <c r="O2" s="4">
+      <c r="P2" s="4">
         <v>0.55555555555555558</v>
       </c>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="2"/>
+      <c r="E3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H3" s="3">
+      <c r="I3" s="3">
         <v>46093</v>
       </c>
-      <c r="I3" s="4">
+      <c r="J3" s="4">
         <v>0.60416666666666663</v>
       </c>
-      <c r="J3" s="5">
+      <c r="K3" s="5">
         <v>46093</v>
       </c>
-      <c r="K3" s="4">
+      <c r="L3" s="4">
         <v>0.65972222222222221</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="N3" s="7">
+      <c r="O3" s="7">
         <v>46093</v>
       </c>
-      <c r="O3" s="4">
+      <c r="P3" s="4">
         <v>0.59722222222222221</v>
       </c>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2" t="s">
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="S3" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="2"/>
+      <c r="E4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="G4" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="3">
+      <c r="I4" s="3">
         <v>46094</v>
       </c>
-      <c r="I4" s="4">
+      <c r="J4" s="4">
         <v>0.64583333333333337</v>
       </c>
-      <c r="J4" s="5">
+      <c r="K4" s="5">
         <v>46094</v>
       </c>
-      <c r="K4" s="4">
+      <c r="L4" s="4">
         <v>0.70138888888888884</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="N4" s="6">
+      <c r="O4" s="6">
         <v>46094</v>
       </c>
-      <c r="O4" s="4">
+      <c r="P4" s="4">
         <v>0.63888888888888884</v>
       </c>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2" t="s">
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="R4" s="1" t="s">
+      <c r="S4" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="2"/>
+      <c r="E5" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H5" s="3">
+      <c r="I5" s="3">
         <v>46095</v>
       </c>
-      <c r="J5" s="5">
+      <c r="K5" s="5">
         <v>46095</v>
       </c>
-      <c r="K5" s="4">
+      <c r="L5" s="4">
         <v>0.74305555555555558</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="M5" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="N5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="N5" s="7">
+      <c r="O5" s="7">
         <v>46095</v>
       </c>
-      <c r="O5" s="4">
+      <c r="P5" s="4">
         <v>0.68055555555555558</v>
       </c>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2" t="s">
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="R5" s="1" t="s">
+      <c r="S5" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="2"/>
+      <c r="E6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="1"/>
       <c r="G6" s="1"/>
-      <c r="H6" s="3">
+      <c r="H6" s="1"/>
+      <c r="I6" s="3">
         <v>46096</v>
       </c>
-      <c r="I6" s="4">
+      <c r="J6" s="4">
         <v>0.6875</v>
       </c>
-      <c r="J6" s="5">
+      <c r="K6" s="5">
         <v>46096</v>
       </c>
-      <c r="K6" s="4"/>
-      <c r="L6" s="1"/>
+      <c r="L6" s="4"/>
       <c r="M6" s="1"/>
-      <c r="N6" s="6">
+      <c r="N6" s="1"/>
+      <c r="O6" s="6">
         <v>46096</v>
       </c>
-      <c r="O6" s="4"/>
-      <c r="P6" s="2"/>
+      <c r="P6" s="4"/>
       <c r="Q6" s="2"/>
-      <c r="R6" s="1" t="s">
+      <c r="R6" s="2"/>
+      <c r="S6" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="2"/>
+      <c r="E7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="1"/>
       <c r="G7" s="1"/>
-      <c r="H7" s="3">
+      <c r="H7" s="1"/>
+      <c r="I7" s="3">
         <v>46097</v>
       </c>
-      <c r="I7" s="4"/>
-      <c r="J7" s="5">
+      <c r="J7" s="4"/>
+      <c r="K7" s="5">
         <v>46097</v>
       </c>
-      <c r="K7" s="4"/>
-      <c r="L7" s="1" t="s">
+      <c r="L7" s="4"/>
+      <c r="M7" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="N7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="N7" s="8">
+      <c r="O7" s="8">
         <v>46097</v>
       </c>
-      <c r="O7" s="4"/>
-      <c r="P7" s="2"/>
+      <c r="P7" s="4"/>
       <c r="Q7" s="2"/>
-      <c r="R7" s="1" t="s">
+      <c r="R7" s="2"/>
+      <c r="S7" s="1" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
-  <dataConsolidate/>
-  <phoneticPr fontId="6" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="K2:K7 O2:O7 I2:I4 I6:I7" xr:uid="{556E1820-0D8B-4C22-87BE-C0B169311AB4}">
-      <formula1>OR(TIMEVALUE(TEXT(I2, "hh:mm:ss"))=I2, AND(ISNUMBER(I2), LEFT(CELL("format", I2))="D"))</formula1>
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="L2:L7 P2:P7 J2:J4 J6:J7" xr:uid="{C3DC2E3E-24BB-4874-8D9F-48A41B506521}">
+      <formula1>OR(TIMEVALUE(TEXT(J2, "hh:mm:ss"))=J2, AND(ISNUMBER(J2), LEFT(CELL("format", J2))="D"))</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="H2:H7 J2:J7" xr:uid="{F8AD7BAB-0343-454D-8A3C-8901E956FB68}">
-      <formula1>OR(NOT(ISERROR(DATEVALUE(H2))), AND(ISNUMBER(H2), LEFT(CELL("format", H2))="D"))</formula1>
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="I2:I7 K2:K7" xr:uid="{F70FCCFB-F801-459A-A1FD-B8986D0402DD}">
+      <formula1>OR(NOT(ISERROR(DATEVALUE(I2))), AND(ISNUMBER(I2), LEFT(CELL("format", I2))="D"))</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="1" sqref="C2:E7 P2:Q7" xr:uid="{5EF31A2A-C3E7-4243-871B-AED7CED1D742}"/>
+    <dataValidation allowBlank="1" showDropDown="1" sqref="D2:F7 Q2:R7" xr:uid="{61AA8E71-8019-489A-AF2A-7FC225294C8D}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -3047,454 +3992,40 @@
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
-        <x14:dataValidation type="list" allowBlank="1" xr:uid="{071DF691-626A-43F5-BBD8-41047158AB08}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{8F1E2BE5-6047-4039-B65C-894C0CAC366E}">
           <x14:formula1>
             <xm:f>'_MAINTENANCE_STATUS'!$B$2:$B$6</xm:f>
           </x14:formula1>
-          <xm:sqref>R2:R7</xm:sqref>
+          <xm:sqref>S2:S7</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" xr:uid="{49863A1B-748B-4998-830A-9601A1683BCA}">
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{63B87D7C-1517-4082-907E-A3FAB5030C9B}">
           <x14:formula1>
-            <xm:f>'_AC_TYPE_LIST'!$B$2:$B$37</xm:f>
+            <xm:f>'_STAFF'!$C$2:$C$131</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B7</xm:sqref>
+          <xm:sqref>M2:N7</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" xr:uid="{1F962603-F644-4495-B25D-6BE423D0DB68}">
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{813938D2-4786-4E76-A5E4-6A991731D538}">
+          <x14:formula1>
+            <xm:f>_ROUTE_LIST!$B$2:$B$27</xm:f>
+          </x14:formula1>
+          <xm:sqref>G2:H7</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{0A434F3D-02F5-4DF3-AC83-775D22C66D4F}">
           <x14:formula1>
             <xm:f>'_AIRLINE_LIST'!$C$2:$C$43</xm:f>
           </x14:formula1>
           <xm:sqref>A2:A7</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" xr:uid="{4C3B29AA-E1A6-4F92-99E4-712C2F9B8471}">
-          <x14:formula1>
-            <xm:f>'_STAFF'!$C$2:$C$131</xm:f>
-          </x14:formula1>
-          <xm:sqref>L2:M7</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" xr:uid="{DE760684-B984-494D-AF51-714EF5DE3E31}">
-          <x14:formula1>
-            <xm:f>_ROUTE_LIST!$B$2:$B$27</xm:f>
-          </x14:formula1>
-          <xm:sqref>F2:G7</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <dimension ref="A1:R7"/>
-  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="23.73046875" customWidth="1"/>
-    <col min="2" max="2" width="27.73046875" customWidth="1"/>
-    <col min="3" max="3" width="19.59765625" customWidth="1"/>
-    <col min="4" max="4" width="26.265625" customWidth="1"/>
-    <col min="5" max="5" width="25.86328125" customWidth="1"/>
-    <col min="6" max="6" width="18.86328125" customWidth="1"/>
-    <col min="7" max="7" width="17.59765625" customWidth="1"/>
-    <col min="8" max="8" width="15.59765625" customWidth="1"/>
-    <col min="9" max="9" width="14.73046875" customWidth="1"/>
-    <col min="10" max="10" width="15.59765625" customWidth="1"/>
-    <col min="11" max="11" width="12.59765625" customWidth="1"/>
-    <col min="12" max="12" width="33.86328125" customWidth="1"/>
-    <col min="13" max="13" width="33.3984375" customWidth="1"/>
-    <col min="14" max="14" width="12.3984375" customWidth="1"/>
-    <col min="15" max="15" width="17.59765625" customWidth="1"/>
-    <col min="16" max="16" width="15.1328125" customWidth="1"/>
-    <col min="17" max="17" width="15.3984375" customWidth="1"/>
-    <col min="18" max="18" width="15.1328125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="15" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H2" s="3">
-        <v>46092</v>
-      </c>
-      <c r="I2" s="4">
-        <v>0.5625</v>
-      </c>
-      <c r="J2" s="5">
-        <v>46092</v>
-      </c>
-      <c r="K2" s="4">
-        <v>0.61805555555555558</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2" s="6">
-        <v>46092</v>
-      </c>
-      <c r="O2" s="4">
-        <v>0.55555555555555558</v>
-      </c>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H3" s="3">
-        <v>46093</v>
-      </c>
-      <c r="I3" s="4">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="J3" s="5">
-        <v>46093</v>
-      </c>
-      <c r="K3" s="4">
-        <v>0.65972222222222221</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="N3" s="7">
-        <v>46093</v>
-      </c>
-      <c r="O3" s="4">
-        <v>0.59722222222222221</v>
-      </c>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>232</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="3">
-        <v>46094</v>
-      </c>
-      <c r="I4" s="4">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="J4" s="5">
-        <v>46094</v>
-      </c>
-      <c r="K4" s="4">
-        <v>0.70138888888888884</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="N4" s="6">
-        <v>46094</v>
-      </c>
-      <c r="O4" s="4">
-        <v>0.63888888888888884</v>
-      </c>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H5" s="3">
-        <v>46095</v>
-      </c>
-      <c r="J5" s="5">
-        <v>46095</v>
-      </c>
-      <c r="K5" s="4">
-        <v>0.74305555555555558</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N5" s="7">
-        <v>46095</v>
-      </c>
-      <c r="O5" s="4">
-        <v>0.68055555555555558</v>
-      </c>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="R5" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="3">
-        <v>46096</v>
-      </c>
-      <c r="I6" s="4">
-        <v>0.6875</v>
-      </c>
-      <c r="J6" s="5">
-        <v>46096</v>
-      </c>
-      <c r="K6" s="4"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="6">
-        <v>46096</v>
-      </c>
-      <c r="O6" s="4"/>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>236</v>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="3">
-        <v>46097</v>
-      </c>
-      <c r="I7" s="4"/>
-      <c r="J7" s="5">
-        <v>46097</v>
-      </c>
-      <c r="K7" s="4"/>
-      <c r="L7" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N7" s="8">
-        <v>46097</v>
-      </c>
-      <c r="O7" s="4"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="3">
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="K2:K7 O2:O7 I2:I4 I6:I7" xr:uid="{D39CCA07-B0D6-4233-AC58-871DA1191B40}">
-      <formula1>OR(TIMEVALUE(TEXT(I2, "hh:mm:ss"))=I2, AND(ISNUMBER(I2), LEFT(CELL("format", I2))="D"))</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="H2:H7 J2:J7" xr:uid="{B36988C3-14AF-435D-BF6E-B7EE46CF9861}">
-      <formula1>OR(NOT(ISERROR(DATEVALUE(H2))), AND(ISNUMBER(H2), LEFT(CELL("format", H2))="D"))</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="1" sqref="C2:E7 P2:Q7" xr:uid="{7FD01062-992C-4C77-ABB6-785C0132E0B2}"/>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
-        <x14:dataValidation type="list" allowBlank="1" xr:uid="{0CB1CA6D-583B-4706-B5E5-86CB845E3EB2}">
-          <x14:formula1>
-            <xm:f>'_MAINTENANCE_STATUS'!$B$2:$B$6</xm:f>
-          </x14:formula1>
-          <xm:sqref>R2:R7</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" xr:uid="{D8DE8933-F3DE-4029-A15E-73D69843E623}">
-          <x14:formula1>
-            <xm:f>'_STAFF'!$C$2:$C$131</xm:f>
-          </x14:formula1>
-          <xm:sqref>L2:M7</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" xr:uid="{81B2B22B-1ED9-448C-9764-39D15443E83D}">
-          <x14:formula1>
-            <xm:f>_ROUTE_LIST!$B$2:$B$27</xm:f>
-          </x14:formula1>
-          <xm:sqref>F2:G7</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" xr:uid="{062CB8B6-8D73-403B-AA5C-38D1759F4DA3}">
-          <x14:formula1>
-            <xm:f>'_AIRLINE_LIST'!$C$2:$C$43</xm:f>
-          </x14:formula1>
-          <xm:sqref>A2:A7</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" xr:uid="{DE60A382-C581-4B11-AFB4-38F9EE4D5CA2}">
+        <x14:dataValidation type="list" xr:uid="{36EBAA40-BCCB-405B-94C4-067EAEB086F8}">
           <x14:formula1>
             <xm:f>'_AC_TYPE_LIST'!$B$2:$B$37</xm:f>
+          </x14:formula1>
+          <xm:sqref>C2:C7</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{DAA652D5-5321-4371-B38D-FCB2D5A08AA0}">
+          <x14:formula1>
+            <xm:f>_STATION_LIST!$B$2:$B$9</xm:f>
           </x14:formula1>
           <xm:sqref>B2:B7</xm:sqref>
         </x14:dataValidation>
@@ -3979,7 +4510,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{171AA897-1BF0-4B78-BE9D-E0D6E90B15D5}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -3987,7 +4518,7 @@
   <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="10.3984375" customWidth="1"/>
-    <col min="3" max="3" width="39.59765625" customWidth="1"/>
+    <col min="3" max="3" width="46.9296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -3998,7 +4529,7 @@
         <v>38</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>56</v>
+        <v>418</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -4020,13 +4551,13 @@
     </row>
     <row r="2" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="20">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>368</v>
+        <v>410</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -4048,13 +4579,13 @@
     </row>
     <row r="3" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>369</v>
+        <v>411</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -4076,13 +4607,13 @@
     </row>
     <row r="4" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>92</v>
+        <v>41</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>370</v>
+        <v>412</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -4104,13 +4635,13 @@
     </row>
     <row r="5" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="20">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>371</v>
+        <v>413</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
@@ -4135,10 +4666,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>91</v>
+        <v>43</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>372</v>
+        <v>414</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
@@ -4160,13 +4691,13 @@
     </row>
     <row r="7" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="20">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>94</v>
+        <v>49</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>373</v>
+        <v>415</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
@@ -4191,10 +4722,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>374</v>
+        <v>416</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
@@ -4216,13 +4747,13 @@
     </row>
     <row r="9" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="20">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>375</v>
+        <v>417</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
@@ -4243,15 +4774,6 @@
       <c r="T9" s="9"/>
     </row>
     <row r="10" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="20">
-        <v>42</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>376</v>
-      </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
@@ -4271,15 +4793,6 @@
       <c r="T10" s="9"/>
     </row>
     <row r="11" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="20">
-        <v>11</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>377</v>
-      </c>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
@@ -4299,15 +4812,6 @@
       <c r="T11" s="9"/>
     </row>
     <row r="12" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="20">
-        <v>40</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>378</v>
-      </c>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
@@ -4327,15 +4831,6 @@
       <c r="T12" s="9"/>
     </row>
     <row r="13" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="20">
-        <v>26</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>379</v>
-      </c>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
@@ -4355,15 +4850,6 @@
       <c r="T13" s="9"/>
     </row>
     <row r="14" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="20">
-        <v>38</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>380</v>
-      </c>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
@@ -4383,15 +4869,6 @@
       <c r="T14" s="9"/>
     </row>
     <row r="15" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="20">
-        <v>47</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>381</v>
-      </c>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
@@ -4411,15 +4888,6 @@
       <c r="T15" s="9"/>
     </row>
     <row r="16" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="20">
-        <v>12</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>382</v>
-      </c>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
@@ -4439,15 +4907,6 @@
       <c r="T16" s="9"/>
     </row>
     <row r="17" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="20">
-        <v>9</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>383</v>
-      </c>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
@@ -4467,15 +4926,6 @@
       <c r="T17" s="9"/>
     </row>
     <row r="18" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="20">
-        <v>13</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>384</v>
-      </c>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
@@ -4495,15 +4945,6 @@
       <c r="T18" s="9"/>
     </row>
     <row r="19" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="20">
-        <v>14</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>385</v>
-      </c>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
@@ -4523,15 +4964,6 @@
       <c r="T19" s="9"/>
     </row>
     <row r="20" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="20">
-        <v>24</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>386</v>
-      </c>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
@@ -4551,15 +4983,6 @@
       <c r="T20" s="9"/>
     </row>
     <row r="21" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="20">
-        <v>1</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>367</v>
-      </c>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
@@ -4579,15 +5002,6 @@
       <c r="T21" s="9"/>
     </row>
     <row r="22" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="20">
-        <v>15</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>387</v>
-      </c>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
@@ -4607,15 +5021,6 @@
       <c r="T22" s="9"/>
     </row>
     <row r="23" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="20">
-        <v>2</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>388</v>
-      </c>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
@@ -4635,15 +5040,6 @@
       <c r="T23" s="9"/>
     </row>
     <row r="24" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="20">
-        <v>10</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>389</v>
-      </c>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
@@ -4663,15 +5059,6 @@
       <c r="T24" s="9"/>
     </row>
     <row r="25" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="20">
-        <v>17</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>390</v>
-      </c>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
@@ -4691,15 +5078,9 @@
       <c r="T25" s="9"/>
     </row>
     <row r="26" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="20">
-        <v>16</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>391</v>
-      </c>
+      <c r="A26" s="20"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="11"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
@@ -4719,15 +5100,9 @@
       <c r="T26" s="9"/>
     </row>
     <row r="27" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="20">
-        <v>18</v>
-      </c>
-      <c r="B27" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>392</v>
-      </c>
+      <c r="A27" s="20"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="11"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
@@ -4747,15 +5122,9 @@
       <c r="T27" s="9"/>
     </row>
     <row r="28" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="20">
-        <v>19</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>393</v>
-      </c>
+      <c r="A28" s="20"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="11"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
@@ -4775,15 +5144,9 @@
       <c r="T28" s="9"/>
     </row>
     <row r="29" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="20">
-        <v>20</v>
-      </c>
-      <c r="B29" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>394</v>
-      </c>
+      <c r="A29" s="20"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="11"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
@@ -4803,15 +5166,9 @@
       <c r="T29" s="9"/>
     </row>
     <row r="30" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="20">
-        <v>21</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>395</v>
-      </c>
+      <c r="A30" s="20"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="11"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
@@ -4831,15 +5188,9 @@
       <c r="T30" s="9"/>
     </row>
     <row r="31" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="20">
-        <v>23</v>
-      </c>
-      <c r="B31" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>396</v>
-      </c>
+      <c r="A31" s="20"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="11"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
@@ -4859,15 +5210,9 @@
       <c r="T31" s="9"/>
     </row>
     <row r="32" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="20">
-        <v>22</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>397</v>
-      </c>
+      <c r="A32" s="20"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="11"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9"/>
@@ -4887,15 +5232,9 @@
       <c r="T32" s="9"/>
     </row>
     <row r="33" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="20">
-        <v>25</v>
-      </c>
-      <c r="B33" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>398</v>
-      </c>
+      <c r="A33" s="20"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="11"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="9"/>
@@ -4915,15 +5254,9 @@
       <c r="T33" s="9"/>
     </row>
     <row r="34" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="20">
-        <v>32</v>
-      </c>
-      <c r="B34" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>399</v>
-      </c>
+      <c r="A34" s="20"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="11"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9"/>
@@ -4943,15 +5276,9 @@
       <c r="T34" s="9"/>
     </row>
     <row r="35" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="20">
-        <v>27</v>
-      </c>
-      <c r="B35" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>400</v>
-      </c>
+      <c r="A35" s="20"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="11"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
       <c r="F35" s="9"/>
@@ -4971,15 +5298,9 @@
       <c r="T35" s="9"/>
     </row>
     <row r="36" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="20">
-        <v>31</v>
-      </c>
-      <c r="B36" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>401</v>
-      </c>
+      <c r="A36" s="20"/>
+      <c r="B36" s="10"/>
+      <c r="C36" s="11"/>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
       <c r="F36" s="9"/>
@@ -4999,15 +5320,9 @@
       <c r="T36" s="9"/>
     </row>
     <row r="37" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="20">
-        <v>35</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>402</v>
-      </c>
+      <c r="A37" s="20"/>
+      <c r="B37" s="10"/>
+      <c r="C37" s="11"/>
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
       <c r="F37" s="9"/>
@@ -5027,15 +5342,9 @@
       <c r="T37" s="9"/>
     </row>
     <row r="38" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="20">
-        <v>29</v>
-      </c>
-      <c r="B38" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>403</v>
-      </c>
+      <c r="A38" s="20"/>
+      <c r="B38" s="10"/>
+      <c r="C38" s="11"/>
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
       <c r="F38" s="9"/>
@@ -5055,15 +5364,9 @@
       <c r="T38" s="9"/>
     </row>
     <row r="39" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="20">
-        <v>37</v>
-      </c>
-      <c r="B39" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>404</v>
-      </c>
+      <c r="A39" s="20"/>
+      <c r="B39" s="10"/>
+      <c r="C39" s="11"/>
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
       <c r="F39" s="9"/>
@@ -5083,15 +5386,9 @@
       <c r="T39" s="9"/>
     </row>
     <row r="40" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="20">
-        <v>39</v>
-      </c>
-      <c r="B40" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="C40" s="11" t="s">
-        <v>405</v>
-      </c>
+      <c r="A40" s="20"/>
+      <c r="B40" s="10"/>
+      <c r="C40" s="11"/>
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
       <c r="F40" s="9"/>
@@ -5111,15 +5408,9 @@
       <c r="T40" s="9"/>
     </row>
     <row r="41" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="20">
-        <v>28</v>
-      </c>
-      <c r="B41" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="C41" s="11" t="s">
-        <v>406</v>
-      </c>
+      <c r="A41" s="20"/>
+      <c r="B41" s="10"/>
+      <c r="C41" s="11"/>
       <c r="D41" s="9"/>
       <c r="E41" s="9"/>
       <c r="F41" s="9"/>
@@ -5139,15 +5430,9 @@
       <c r="T41" s="9"/>
     </row>
     <row r="42" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="20">
-        <v>34</v>
-      </c>
-      <c r="B42" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C42" s="11" t="s">
-        <v>407</v>
-      </c>
+      <c r="A42" s="20"/>
+      <c r="B42" s="10"/>
+      <c r="C42" s="11"/>
       <c r="D42" s="9"/>
       <c r="E42" s="9"/>
       <c r="F42" s="9"/>
@@ -5167,6 +5452,1210 @@
       <c r="T42" s="9"/>
     </row>
     <row r="43" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="20"/>
+      <c r="B43" s="18"/>
+      <c r="C43" s="19"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation allowBlank="1" showDropDown="1" sqref="B2:C9 B26:C43" xr:uid="{62B7F2C8-2397-4CAD-8F63-FF06BA4C0B3A}"/>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:T43"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="2" width="10.3984375" customWidth="1"/>
+    <col min="3" max="3" width="39.59765625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+    </row>
+    <row r="2" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="20">
+        <v>8</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>368</v>
+      </c>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+    </row>
+    <row r="3" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="20">
+        <v>3</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>369</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+    </row>
+    <row r="4" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="20">
+        <v>6</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+    </row>
+    <row r="5" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="20">
+        <v>30</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>371</v>
+      </c>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="9"/>
+    </row>
+    <row r="6" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="20">
+        <v>5</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>372</v>
+      </c>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="9"/>
+      <c r="R6" s="9"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="9"/>
+    </row>
+    <row r="7" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="20">
+        <v>4</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="9"/>
+      <c r="S7" s="9"/>
+      <c r="T7" s="9"/>
+    </row>
+    <row r="8" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="20">
+        <v>7</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="9"/>
+      <c r="R8" s="9"/>
+      <c r="S8" s="9"/>
+      <c r="T8" s="9"/>
+    </row>
+    <row r="9" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="20">
+        <v>33</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>375</v>
+      </c>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="9"/>
+      <c r="R9" s="9"/>
+      <c r="S9" s="9"/>
+      <c r="T9" s="9"/>
+    </row>
+    <row r="10" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="20">
+        <v>42</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="9"/>
+      <c r="O10" s="9"/>
+      <c r="P10" s="9"/>
+      <c r="Q10" s="9"/>
+      <c r="R10" s="9"/>
+      <c r="S10" s="9"/>
+      <c r="T10" s="9"/>
+    </row>
+    <row r="11" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="20">
+        <v>11</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>377</v>
+      </c>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="9"/>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="9"/>
+      <c r="R11" s="9"/>
+      <c r="S11" s="9"/>
+      <c r="T11" s="9"/>
+    </row>
+    <row r="12" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="20">
+        <v>40</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>378</v>
+      </c>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="9"/>
+      <c r="P12" s="9"/>
+      <c r="Q12" s="9"/>
+      <c r="R12" s="9"/>
+      <c r="S12" s="9"/>
+      <c r="T12" s="9"/>
+    </row>
+    <row r="13" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="20">
+        <v>26</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>379</v>
+      </c>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="9"/>
+      <c r="P13" s="9"/>
+      <c r="Q13" s="9"/>
+      <c r="R13" s="9"/>
+      <c r="S13" s="9"/>
+      <c r="T13" s="9"/>
+    </row>
+    <row r="14" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="20">
+        <v>38</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>380</v>
+      </c>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
+      <c r="P14" s="9"/>
+      <c r="Q14" s="9"/>
+      <c r="R14" s="9"/>
+      <c r="S14" s="9"/>
+      <c r="T14" s="9"/>
+    </row>
+    <row r="15" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="20">
+        <v>47</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>381</v>
+      </c>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="9"/>
+      <c r="P15" s="9"/>
+      <c r="Q15" s="9"/>
+      <c r="R15" s="9"/>
+      <c r="S15" s="9"/>
+      <c r="T15" s="9"/>
+    </row>
+    <row r="16" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="20">
+        <v>12</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>382</v>
+      </c>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="9"/>
+      <c r="P16" s="9"/>
+      <c r="Q16" s="9"/>
+      <c r="R16" s="9"/>
+      <c r="S16" s="9"/>
+      <c r="T16" s="9"/>
+    </row>
+    <row r="17" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="20">
+        <v>9</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="9"/>
+      <c r="P17" s="9"/>
+      <c r="Q17" s="9"/>
+      <c r="R17" s="9"/>
+      <c r="S17" s="9"/>
+      <c r="T17" s="9"/>
+    </row>
+    <row r="18" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="20">
+        <v>13</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>384</v>
+      </c>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="9"/>
+      <c r="Q18" s="9"/>
+      <c r="R18" s="9"/>
+      <c r="S18" s="9"/>
+      <c r="T18" s="9"/>
+    </row>
+    <row r="19" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="20">
+        <v>14</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>385</v>
+      </c>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="9"/>
+      <c r="O19" s="9"/>
+      <c r="P19" s="9"/>
+      <c r="Q19" s="9"/>
+      <c r="R19" s="9"/>
+      <c r="S19" s="9"/>
+      <c r="T19" s="9"/>
+    </row>
+    <row r="20" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="20">
+        <v>24</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>386</v>
+      </c>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="9"/>
+      <c r="N20" s="9"/>
+      <c r="O20" s="9"/>
+      <c r="P20" s="9"/>
+      <c r="Q20" s="9"/>
+      <c r="R20" s="9"/>
+      <c r="S20" s="9"/>
+      <c r="T20" s="9"/>
+    </row>
+    <row r="21" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="20">
+        <v>1</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="9"/>
+      <c r="N21" s="9"/>
+      <c r="O21" s="9"/>
+      <c r="P21" s="9"/>
+      <c r="Q21" s="9"/>
+      <c r="R21" s="9"/>
+      <c r="S21" s="9"/>
+      <c r="T21" s="9"/>
+    </row>
+    <row r="22" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="20">
+        <v>15</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>387</v>
+      </c>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+      <c r="M22" s="9"/>
+      <c r="N22" s="9"/>
+      <c r="O22" s="9"/>
+      <c r="P22" s="9"/>
+      <c r="Q22" s="9"/>
+      <c r="R22" s="9"/>
+      <c r="S22" s="9"/>
+      <c r="T22" s="9"/>
+    </row>
+    <row r="23" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="20">
+        <v>2</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>388</v>
+      </c>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9"/>
+      <c r="M23" s="9"/>
+      <c r="N23" s="9"/>
+      <c r="O23" s="9"/>
+      <c r="P23" s="9"/>
+      <c r="Q23" s="9"/>
+      <c r="R23" s="9"/>
+      <c r="S23" s="9"/>
+      <c r="T23" s="9"/>
+    </row>
+    <row r="24" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="20">
+        <v>10</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>389</v>
+      </c>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
+      <c r="M24" s="9"/>
+      <c r="N24" s="9"/>
+      <c r="O24" s="9"/>
+      <c r="P24" s="9"/>
+      <c r="Q24" s="9"/>
+      <c r="R24" s="9"/>
+      <c r="S24" s="9"/>
+      <c r="T24" s="9"/>
+    </row>
+    <row r="25" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="20">
+        <v>17</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>390</v>
+      </c>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="9"/>
+      <c r="O25" s="9"/>
+      <c r="P25" s="9"/>
+      <c r="Q25" s="9"/>
+      <c r="R25" s="9"/>
+      <c r="S25" s="9"/>
+      <c r="T25" s="9"/>
+    </row>
+    <row r="26" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="20">
+        <v>16</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="9"/>
+      <c r="O26" s="9"/>
+      <c r="P26" s="9"/>
+      <c r="Q26" s="9"/>
+      <c r="R26" s="9"/>
+      <c r="S26" s="9"/>
+      <c r="T26" s="9"/>
+    </row>
+    <row r="27" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="20">
+        <v>18</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>392</v>
+      </c>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
+      <c r="M27" s="9"/>
+      <c r="N27" s="9"/>
+      <c r="O27" s="9"/>
+      <c r="P27" s="9"/>
+      <c r="Q27" s="9"/>
+      <c r="R27" s="9"/>
+      <c r="S27" s="9"/>
+      <c r="T27" s="9"/>
+    </row>
+    <row r="28" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="20">
+        <v>19</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>393</v>
+      </c>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
+      <c r="M28" s="9"/>
+      <c r="N28" s="9"/>
+      <c r="O28" s="9"/>
+      <c r="P28" s="9"/>
+      <c r="Q28" s="9"/>
+      <c r="R28" s="9"/>
+      <c r="S28" s="9"/>
+      <c r="T28" s="9"/>
+    </row>
+    <row r="29" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="20">
+        <v>20</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>394</v>
+      </c>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="9"/>
+      <c r="M29" s="9"/>
+      <c r="N29" s="9"/>
+      <c r="O29" s="9"/>
+      <c r="P29" s="9"/>
+      <c r="Q29" s="9"/>
+      <c r="R29" s="9"/>
+      <c r="S29" s="9"/>
+      <c r="T29" s="9"/>
+    </row>
+    <row r="30" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="20">
+        <v>21</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>395</v>
+      </c>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="9"/>
+      <c r="M30" s="9"/>
+      <c r="N30" s="9"/>
+      <c r="O30" s="9"/>
+      <c r="P30" s="9"/>
+      <c r="Q30" s="9"/>
+      <c r="R30" s="9"/>
+      <c r="S30" s="9"/>
+      <c r="T30" s="9"/>
+    </row>
+    <row r="31" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="20">
+        <v>23</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>396</v>
+      </c>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="9"/>
+      <c r="M31" s="9"/>
+      <c r="N31" s="9"/>
+      <c r="O31" s="9"/>
+      <c r="P31" s="9"/>
+      <c r="Q31" s="9"/>
+      <c r="R31" s="9"/>
+      <c r="S31" s="9"/>
+      <c r="T31" s="9"/>
+    </row>
+    <row r="32" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="20">
+        <v>22</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>397</v>
+      </c>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="9"/>
+      <c r="M32" s="9"/>
+      <c r="N32" s="9"/>
+      <c r="O32" s="9"/>
+      <c r="P32" s="9"/>
+      <c r="Q32" s="9"/>
+      <c r="R32" s="9"/>
+      <c r="S32" s="9"/>
+      <c r="T32" s="9"/>
+    </row>
+    <row r="33" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="20">
+        <v>25</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>398</v>
+      </c>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="9"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="9"/>
+      <c r="M33" s="9"/>
+      <c r="N33" s="9"/>
+      <c r="O33" s="9"/>
+      <c r="P33" s="9"/>
+      <c r="Q33" s="9"/>
+      <c r="R33" s="9"/>
+      <c r="S33" s="9"/>
+      <c r="T33" s="9"/>
+    </row>
+    <row r="34" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="20">
+        <v>32</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="9"/>
+      <c r="K34" s="9"/>
+      <c r="L34" s="9"/>
+      <c r="M34" s="9"/>
+      <c r="N34" s="9"/>
+      <c r="O34" s="9"/>
+      <c r="P34" s="9"/>
+      <c r="Q34" s="9"/>
+      <c r="R34" s="9"/>
+      <c r="S34" s="9"/>
+      <c r="T34" s="9"/>
+    </row>
+    <row r="35" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="20">
+        <v>27</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="9"/>
+      <c r="K35" s="9"/>
+      <c r="L35" s="9"/>
+      <c r="M35" s="9"/>
+      <c r="N35" s="9"/>
+      <c r="O35" s="9"/>
+      <c r="P35" s="9"/>
+      <c r="Q35" s="9"/>
+      <c r="R35" s="9"/>
+      <c r="S35" s="9"/>
+      <c r="T35" s="9"/>
+    </row>
+    <row r="36" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="20">
+        <v>31</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>401</v>
+      </c>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="9"/>
+      <c r="J36" s="9"/>
+      <c r="K36" s="9"/>
+      <c r="L36" s="9"/>
+      <c r="M36" s="9"/>
+      <c r="N36" s="9"/>
+      <c r="O36" s="9"/>
+      <c r="P36" s="9"/>
+      <c r="Q36" s="9"/>
+      <c r="R36" s="9"/>
+      <c r="S36" s="9"/>
+      <c r="T36" s="9"/>
+    </row>
+    <row r="37" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="20">
+        <v>35</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>402</v>
+      </c>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="9"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="9"/>
+      <c r="M37" s="9"/>
+      <c r="N37" s="9"/>
+      <c r="O37" s="9"/>
+      <c r="P37" s="9"/>
+      <c r="Q37" s="9"/>
+      <c r="R37" s="9"/>
+      <c r="S37" s="9"/>
+      <c r="T37" s="9"/>
+    </row>
+    <row r="38" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="20">
+        <v>29</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>403</v>
+      </c>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="9"/>
+      <c r="K38" s="9"/>
+      <c r="L38" s="9"/>
+      <c r="M38" s="9"/>
+      <c r="N38" s="9"/>
+      <c r="O38" s="9"/>
+      <c r="P38" s="9"/>
+      <c r="Q38" s="9"/>
+      <c r="R38" s="9"/>
+      <c r="S38" s="9"/>
+      <c r="T38" s="9"/>
+    </row>
+    <row r="39" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="20">
+        <v>37</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>404</v>
+      </c>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="9"/>
+      <c r="I39" s="9"/>
+      <c r="J39" s="9"/>
+      <c r="K39" s="9"/>
+      <c r="L39" s="9"/>
+      <c r="M39" s="9"/>
+      <c r="N39" s="9"/>
+      <c r="O39" s="9"/>
+      <c r="P39" s="9"/>
+      <c r="Q39" s="9"/>
+      <c r="R39" s="9"/>
+      <c r="S39" s="9"/>
+      <c r="T39" s="9"/>
+    </row>
+    <row r="40" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="20">
+        <v>39</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>405</v>
+      </c>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="9"/>
+      <c r="K40" s="9"/>
+      <c r="L40" s="9"/>
+      <c r="M40" s="9"/>
+      <c r="N40" s="9"/>
+      <c r="O40" s="9"/>
+      <c r="P40" s="9"/>
+      <c r="Q40" s="9"/>
+      <c r="R40" s="9"/>
+      <c r="S40" s="9"/>
+      <c r="T40" s="9"/>
+    </row>
+    <row r="41" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="20">
+        <v>28</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>406</v>
+      </c>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
+      <c r="J41" s="9"/>
+      <c r="K41" s="9"/>
+      <c r="L41" s="9"/>
+      <c r="M41" s="9"/>
+      <c r="N41" s="9"/>
+      <c r="O41" s="9"/>
+      <c r="P41" s="9"/>
+      <c r="Q41" s="9"/>
+      <c r="R41" s="9"/>
+      <c r="S41" s="9"/>
+      <c r="T41" s="9"/>
+    </row>
+    <row r="42" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="20">
+        <v>34</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>407</v>
+      </c>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="9"/>
+      <c r="I42" s="9"/>
+      <c r="J42" s="9"/>
+      <c r="K42" s="9"/>
+      <c r="L42" s="9"/>
+      <c r="M42" s="9"/>
+      <c r="N42" s="9"/>
+      <c r="O42" s="9"/>
+      <c r="P42" s="9"/>
+      <c r="Q42" s="9"/>
+      <c r="R42" s="9"/>
+      <c r="S42" s="9"/>
+      <c r="T42" s="9"/>
+    </row>
+    <row r="43" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="20">
         <v>41</v>
       </c>
@@ -5188,7 +6677,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -5619,7 +7108,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
